--- a/data/random_seed.xlsx
+++ b/data/random_seed.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7827"/>
+  <dimension ref="A1:A8317"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -39490,6 +39490,2456 @@
     <row r="7827">
       <c r="A7827">
         <v>185031309</v>
+      </c>
+    </row>
+    <row r="7828">
+      <c r="A7828">
+        <v>2046946416</v>
+      </c>
+    </row>
+    <row r="7829">
+      <c r="A7829">
+        <v>1505747099</v>
+      </c>
+    </row>
+    <row r="7830">
+      <c r="A7830">
+        <v>521612518</v>
+      </c>
+    </row>
+    <row r="7831">
+      <c r="A7831">
+        <v>1054491022</v>
+      </c>
+    </row>
+    <row r="7832">
+      <c r="A7832">
+        <v>896448815</v>
+      </c>
+    </row>
+    <row r="7833">
+      <c r="A7833">
+        <v>878623542</v>
+      </c>
+    </row>
+    <row r="7834">
+      <c r="A7834">
+        <v>1770800094</v>
+      </c>
+    </row>
+    <row r="7835">
+      <c r="A7835">
+        <v>739563068</v>
+      </c>
+    </row>
+    <row r="7836">
+      <c r="A7836">
+        <v>185727145</v>
+      </c>
+    </row>
+    <row r="7837">
+      <c r="A7837">
+        <v>170031275</v>
+      </c>
+    </row>
+    <row r="7838">
+      <c r="A7838">
+        <v>585928344</v>
+      </c>
+    </row>
+    <row r="7839">
+      <c r="A7839">
+        <v>1480596876</v>
+      </c>
+    </row>
+    <row r="7840">
+      <c r="A7840">
+        <v>710883366</v>
+      </c>
+    </row>
+    <row r="7841">
+      <c r="A7841">
+        <v>183714870</v>
+      </c>
+    </row>
+    <row r="7842">
+      <c r="A7842">
+        <v>2023399732</v>
+      </c>
+    </row>
+    <row r="7843">
+      <c r="A7843">
+        <v>474547585</v>
+      </c>
+    </row>
+    <row r="7844">
+      <c r="A7844">
+        <v>570568715</v>
+      </c>
+    </row>
+    <row r="7845">
+      <c r="A7845">
+        <v>2089202335</v>
+      </c>
+    </row>
+    <row r="7846">
+      <c r="A7846">
+        <v>509518977</v>
+      </c>
+    </row>
+    <row r="7847">
+      <c r="A7847">
+        <v>1645727262</v>
+      </c>
+    </row>
+    <row r="7848">
+      <c r="A7848">
+        <v>1707889895</v>
+      </c>
+    </row>
+    <row r="7849">
+      <c r="A7849">
+        <v>1040951699</v>
+      </c>
+    </row>
+    <row r="7850">
+      <c r="A7850">
+        <v>490323296</v>
+      </c>
+    </row>
+    <row r="7851">
+      <c r="A7851">
+        <v>25895916</v>
+      </c>
+    </row>
+    <row r="7852">
+      <c r="A7852">
+        <v>1060396584</v>
+      </c>
+    </row>
+    <row r="7853">
+      <c r="A7853">
+        <v>1556574204</v>
+      </c>
+    </row>
+    <row r="7854">
+      <c r="A7854">
+        <v>247754981</v>
+      </c>
+    </row>
+    <row r="7855">
+      <c r="A7855">
+        <v>404142654</v>
+      </c>
+    </row>
+    <row r="7856">
+      <c r="A7856">
+        <v>184640952</v>
+      </c>
+    </row>
+    <row r="7857">
+      <c r="A7857">
+        <v>513853270</v>
+      </c>
+    </row>
+    <row r="7858">
+      <c r="A7858">
+        <v>81596608</v>
+      </c>
+    </row>
+    <row r="7859">
+      <c r="A7859">
+        <v>2018589524</v>
+      </c>
+    </row>
+    <row r="7860">
+      <c r="A7860">
+        <v>913319880</v>
+      </c>
+    </row>
+    <row r="7861">
+      <c r="A7861">
+        <v>2042083709</v>
+      </c>
+    </row>
+    <row r="7862">
+      <c r="A7862">
+        <v>1705740665</v>
+      </c>
+    </row>
+    <row r="7863">
+      <c r="A7863">
+        <v>117419205</v>
+      </c>
+    </row>
+    <row r="7864">
+      <c r="A7864">
+        <v>268424261</v>
+      </c>
+    </row>
+    <row r="7865">
+      <c r="A7865">
+        <v>1836239411</v>
+      </c>
+    </row>
+    <row r="7866">
+      <c r="A7866">
+        <v>2033530570</v>
+      </c>
+    </row>
+    <row r="7867">
+      <c r="A7867">
+        <v>1134241227</v>
+      </c>
+    </row>
+    <row r="7868">
+      <c r="A7868">
+        <v>1852929409</v>
+      </c>
+    </row>
+    <row r="7869">
+      <c r="A7869">
+        <v>866095758</v>
+      </c>
+    </row>
+    <row r="7870">
+      <c r="A7870">
+        <v>2033674482</v>
+      </c>
+    </row>
+    <row r="7871">
+      <c r="A7871">
+        <v>1160866689</v>
+      </c>
+    </row>
+    <row r="7872">
+      <c r="A7872">
+        <v>818702439</v>
+      </c>
+    </row>
+    <row r="7873">
+      <c r="A7873">
+        <v>1112221620</v>
+      </c>
+    </row>
+    <row r="7874">
+      <c r="A7874">
+        <v>2091701077</v>
+      </c>
+    </row>
+    <row r="7875">
+      <c r="A7875">
+        <v>1998297417</v>
+      </c>
+    </row>
+    <row r="7876">
+      <c r="A7876">
+        <v>1949868622</v>
+      </c>
+    </row>
+    <row r="7877">
+      <c r="A7877">
+        <v>33584137</v>
+      </c>
+    </row>
+    <row r="7878">
+      <c r="A7878">
+        <v>416562294</v>
+      </c>
+    </row>
+    <row r="7879">
+      <c r="A7879">
+        <v>667090434</v>
+      </c>
+    </row>
+    <row r="7880">
+      <c r="A7880">
+        <v>738150210</v>
+      </c>
+    </row>
+    <row r="7881">
+      <c r="A7881">
+        <v>391135942</v>
+      </c>
+    </row>
+    <row r="7882">
+      <c r="A7882">
+        <v>1662917442</v>
+      </c>
+    </row>
+    <row r="7883">
+      <c r="A7883">
+        <v>1092648834</v>
+      </c>
+    </row>
+    <row r="7884">
+      <c r="A7884">
+        <v>1382321661</v>
+      </c>
+    </row>
+    <row r="7885">
+      <c r="A7885">
+        <v>1528190924</v>
+      </c>
+    </row>
+    <row r="7886">
+      <c r="A7886">
+        <v>810333685</v>
+      </c>
+    </row>
+    <row r="7887">
+      <c r="A7887">
+        <v>2120962998</v>
+      </c>
+    </row>
+    <row r="7888">
+      <c r="A7888">
+        <v>216762244</v>
+      </c>
+    </row>
+    <row r="7889">
+      <c r="A7889">
+        <v>362605592</v>
+      </c>
+    </row>
+    <row r="7890">
+      <c r="A7890">
+        <v>1366162049</v>
+      </c>
+    </row>
+    <row r="7891">
+      <c r="A7891">
+        <v>1209798996</v>
+      </c>
+    </row>
+    <row r="7892">
+      <c r="A7892">
+        <v>1481988724</v>
+      </c>
+    </row>
+    <row r="7893">
+      <c r="A7893">
+        <v>551449177</v>
+      </c>
+    </row>
+    <row r="7894">
+      <c r="A7894">
+        <v>216636201</v>
+      </c>
+    </row>
+    <row r="7895">
+      <c r="A7895">
+        <v>911004881</v>
+      </c>
+    </row>
+    <row r="7896">
+      <c r="A7896">
+        <v>1506675902</v>
+      </c>
+    </row>
+    <row r="7897">
+      <c r="A7897">
+        <v>1602547332</v>
+      </c>
+    </row>
+    <row r="7898">
+      <c r="A7898">
+        <v>194649533</v>
+      </c>
+    </row>
+    <row r="7899">
+      <c r="A7899">
+        <v>1464847555</v>
+      </c>
+    </row>
+    <row r="7900">
+      <c r="A7900">
+        <v>1230323411</v>
+      </c>
+    </row>
+    <row r="7901">
+      <c r="A7901">
+        <v>1223827732</v>
+      </c>
+    </row>
+    <row r="7902">
+      <c r="A7902">
+        <v>292186306</v>
+      </c>
+    </row>
+    <row r="7903">
+      <c r="A7903">
+        <v>1644946757</v>
+      </c>
+    </row>
+    <row r="7904">
+      <c r="A7904">
+        <v>819846418</v>
+      </c>
+    </row>
+    <row r="7905">
+      <c r="A7905">
+        <v>1618416988</v>
+      </c>
+    </row>
+    <row r="7906">
+      <c r="A7906">
+        <v>1735759073</v>
+      </c>
+    </row>
+    <row r="7907">
+      <c r="A7907">
+        <v>150177657</v>
+      </c>
+    </row>
+    <row r="7908">
+      <c r="A7908">
+        <v>929276091</v>
+      </c>
+    </row>
+    <row r="7909">
+      <c r="A7909">
+        <v>1976465781</v>
+      </c>
+    </row>
+    <row r="7910">
+      <c r="A7910">
+        <v>1167313449</v>
+      </c>
+    </row>
+    <row r="7911">
+      <c r="A7911">
+        <v>2146628822</v>
+      </c>
+    </row>
+    <row r="7912">
+      <c r="A7912">
+        <v>1658440758</v>
+      </c>
+    </row>
+    <row r="7913">
+      <c r="A7913">
+        <v>1526887883</v>
+      </c>
+    </row>
+    <row r="7914">
+      <c r="A7914">
+        <v>1014828667</v>
+      </c>
+    </row>
+    <row r="7915">
+      <c r="A7915">
+        <v>455448666</v>
+      </c>
+    </row>
+    <row r="7916">
+      <c r="A7916">
+        <v>672690647</v>
+      </c>
+    </row>
+    <row r="7917">
+      <c r="A7917">
+        <v>1644384570</v>
+      </c>
+    </row>
+    <row r="7918">
+      <c r="A7918">
+        <v>532920314</v>
+      </c>
+    </row>
+    <row r="7919">
+      <c r="A7919">
+        <v>1576723231</v>
+      </c>
+    </row>
+    <row r="7920">
+      <c r="A7920">
+        <v>1873591081</v>
+      </c>
+    </row>
+    <row r="7921">
+      <c r="A7921">
+        <v>895441761</v>
+      </c>
+    </row>
+    <row r="7922">
+      <c r="A7922">
+        <v>2074317756</v>
+      </c>
+    </row>
+    <row r="7923">
+      <c r="A7923">
+        <v>730503523</v>
+      </c>
+    </row>
+    <row r="7924">
+      <c r="A7924">
+        <v>1045628954</v>
+      </c>
+    </row>
+    <row r="7925">
+      <c r="A7925">
+        <v>894557040</v>
+      </c>
+    </row>
+    <row r="7926">
+      <c r="A7926">
+        <v>887587549</v>
+      </c>
+    </row>
+    <row r="7927">
+      <c r="A7927">
+        <v>1511365085</v>
+      </c>
+    </row>
+    <row r="7928">
+      <c r="A7928">
+        <v>1338494134</v>
+      </c>
+    </row>
+    <row r="7929">
+      <c r="A7929">
+        <v>1145123673</v>
+      </c>
+    </row>
+    <row r="7930">
+      <c r="A7930">
+        <v>855283358</v>
+      </c>
+    </row>
+    <row r="7931">
+      <c r="A7931">
+        <v>517400609</v>
+      </c>
+    </row>
+    <row r="7932">
+      <c r="A7932">
+        <v>1562516337</v>
+      </c>
+    </row>
+    <row r="7933">
+      <c r="A7933">
+        <v>1499063340</v>
+      </c>
+    </row>
+    <row r="7934">
+      <c r="A7934">
+        <v>2087192516</v>
+      </c>
+    </row>
+    <row r="7935">
+      <c r="A7935">
+        <v>1848779347</v>
+      </c>
+    </row>
+    <row r="7936">
+      <c r="A7936">
+        <v>724888595</v>
+      </c>
+    </row>
+    <row r="7937">
+      <c r="A7937">
+        <v>775935813</v>
+      </c>
+    </row>
+    <row r="7938">
+      <c r="A7938">
+        <v>218361742</v>
+      </c>
+    </row>
+    <row r="7939">
+      <c r="A7939">
+        <v>1945658611</v>
+      </c>
+    </row>
+    <row r="7940">
+      <c r="A7940">
+        <v>574386408</v>
+      </c>
+    </row>
+    <row r="7941">
+      <c r="A7941">
+        <v>548652858</v>
+      </c>
+    </row>
+    <row r="7942">
+      <c r="A7942">
+        <v>92006653</v>
+      </c>
+    </row>
+    <row r="7943">
+      <c r="A7943">
+        <v>1889597591</v>
+      </c>
+    </row>
+    <row r="7944">
+      <c r="A7944">
+        <v>443836089</v>
+      </c>
+    </row>
+    <row r="7945">
+      <c r="A7945">
+        <v>1113389929</v>
+      </c>
+    </row>
+    <row r="7946">
+      <c r="A7946">
+        <v>1819476352</v>
+      </c>
+    </row>
+    <row r="7947">
+      <c r="A7947">
+        <v>286433057</v>
+      </c>
+    </row>
+    <row r="7948">
+      <c r="A7948">
+        <v>173003109</v>
+      </c>
+    </row>
+    <row r="7949">
+      <c r="A7949">
+        <v>2030969279</v>
+      </c>
+    </row>
+    <row r="7950">
+      <c r="A7950">
+        <v>108626293</v>
+      </c>
+    </row>
+    <row r="7951">
+      <c r="A7951">
+        <v>407939911</v>
+      </c>
+    </row>
+    <row r="7952">
+      <c r="A7952">
+        <v>220073309</v>
+      </c>
+    </row>
+    <row r="7953">
+      <c r="A7953">
+        <v>129750276</v>
+      </c>
+    </row>
+    <row r="7954">
+      <c r="A7954">
+        <v>613386219</v>
+      </c>
+    </row>
+    <row r="7955">
+      <c r="A7955">
+        <v>1162416439</v>
+      </c>
+    </row>
+    <row r="7956">
+      <c r="A7956">
+        <v>1100360222</v>
+      </c>
+    </row>
+    <row r="7957">
+      <c r="A7957">
+        <v>1398760183</v>
+      </c>
+    </row>
+    <row r="7958">
+      <c r="A7958">
+        <v>590737103</v>
+      </c>
+    </row>
+    <row r="7959">
+      <c r="A7959">
+        <v>91656971</v>
+      </c>
+    </row>
+    <row r="7960">
+      <c r="A7960">
+        <v>1709964033</v>
+      </c>
+    </row>
+    <row r="7961">
+      <c r="A7961">
+        <v>1880325905</v>
+      </c>
+    </row>
+    <row r="7962">
+      <c r="A7962">
+        <v>618299637</v>
+      </c>
+    </row>
+    <row r="7963">
+      <c r="A7963">
+        <v>2130511680</v>
+      </c>
+    </row>
+    <row r="7964">
+      <c r="A7964">
+        <v>2135399761</v>
+      </c>
+    </row>
+    <row r="7965">
+      <c r="A7965">
+        <v>361770162</v>
+      </c>
+    </row>
+    <row r="7966">
+      <c r="A7966">
+        <v>1742470311</v>
+      </c>
+    </row>
+    <row r="7967">
+      <c r="A7967">
+        <v>72372952</v>
+      </c>
+    </row>
+    <row r="7968">
+      <c r="A7968">
+        <v>713384265</v>
+      </c>
+    </row>
+    <row r="7969">
+      <c r="A7969">
+        <v>1283071534</v>
+      </c>
+    </row>
+    <row r="7970">
+      <c r="A7970">
+        <v>1643956407</v>
+      </c>
+    </row>
+    <row r="7971">
+      <c r="A7971">
+        <v>32996656</v>
+      </c>
+    </row>
+    <row r="7972">
+      <c r="A7972">
+        <v>563338968</v>
+      </c>
+    </row>
+    <row r="7973">
+      <c r="A7973">
+        <v>2141831341</v>
+      </c>
+    </row>
+    <row r="7974">
+      <c r="A7974">
+        <v>1749312837</v>
+      </c>
+    </row>
+    <row r="7975">
+      <c r="A7975">
+        <v>868579449</v>
+      </c>
+    </row>
+    <row r="7976">
+      <c r="A7976">
+        <v>1010999187</v>
+      </c>
+    </row>
+    <row r="7977">
+      <c r="A7977">
+        <v>1999048454</v>
+      </c>
+    </row>
+    <row r="7978">
+      <c r="A7978">
+        <v>1752370477</v>
+      </c>
+    </row>
+    <row r="7979">
+      <c r="A7979">
+        <v>811771206</v>
+      </c>
+    </row>
+    <row r="7980">
+      <c r="A7980">
+        <v>1074277445</v>
+      </c>
+    </row>
+    <row r="7981">
+      <c r="A7981">
+        <v>129702967</v>
+      </c>
+    </row>
+    <row r="7982">
+      <c r="A7982">
+        <v>1716554360</v>
+      </c>
+    </row>
+    <row r="7983">
+      <c r="A7983">
+        <v>883864354</v>
+      </c>
+    </row>
+    <row r="7984">
+      <c r="A7984">
+        <v>258383196</v>
+      </c>
+    </row>
+    <row r="7985">
+      <c r="A7985">
+        <v>849538645</v>
+      </c>
+    </row>
+    <row r="7986">
+      <c r="A7986">
+        <v>2079395428</v>
+      </c>
+    </row>
+    <row r="7987">
+      <c r="A7987">
+        <v>59568137</v>
+      </c>
+    </row>
+    <row r="7988">
+      <c r="A7988">
+        <v>546741008</v>
+      </c>
+    </row>
+    <row r="7989">
+      <c r="A7989">
+        <v>732901573</v>
+      </c>
+    </row>
+    <row r="7990">
+      <c r="A7990">
+        <v>215604922</v>
+      </c>
+    </row>
+    <row r="7991">
+      <c r="A7991">
+        <v>385729235</v>
+      </c>
+    </row>
+    <row r="7992">
+      <c r="A7992">
+        <v>835201561</v>
+      </c>
+    </row>
+    <row r="7993">
+      <c r="A7993">
+        <v>279813722</v>
+      </c>
+    </row>
+    <row r="7994">
+      <c r="A7994">
+        <v>1570696486</v>
+      </c>
+    </row>
+    <row r="7995">
+      <c r="A7995">
+        <v>1087637</v>
+      </c>
+    </row>
+    <row r="7996">
+      <c r="A7996">
+        <v>1199946225</v>
+      </c>
+    </row>
+    <row r="7997">
+      <c r="A7997">
+        <v>2056496872</v>
+      </c>
+    </row>
+    <row r="7998">
+      <c r="A7998">
+        <v>1818498415</v>
+      </c>
+    </row>
+    <row r="7999">
+      <c r="A7999">
+        <v>465466789</v>
+      </c>
+    </row>
+    <row r="8000">
+      <c r="A8000">
+        <v>27311814</v>
+      </c>
+    </row>
+    <row r="8001">
+      <c r="A8001">
+        <v>2037971975</v>
+      </c>
+    </row>
+    <row r="8002">
+      <c r="A8002">
+        <v>1522148921</v>
+      </c>
+    </row>
+    <row r="8003">
+      <c r="A8003">
+        <v>594685104</v>
+      </c>
+    </row>
+    <row r="8004">
+      <c r="A8004">
+        <v>325341865</v>
+      </c>
+    </row>
+    <row r="8005">
+      <c r="A8005">
+        <v>1187385492</v>
+      </c>
+    </row>
+    <row r="8006">
+      <c r="A8006">
+        <v>1654752855</v>
+      </c>
+    </row>
+    <row r="8007">
+      <c r="A8007">
+        <v>895383345</v>
+      </c>
+    </row>
+    <row r="8008">
+      <c r="A8008">
+        <v>2057929674</v>
+      </c>
+    </row>
+    <row r="8009">
+      <c r="A8009">
+        <v>1938416301</v>
+      </c>
+    </row>
+    <row r="8010">
+      <c r="A8010">
+        <v>105473727</v>
+      </c>
+    </row>
+    <row r="8011">
+      <c r="A8011">
+        <v>2044166391</v>
+      </c>
+    </row>
+    <row r="8012">
+      <c r="A8012">
+        <v>1356923745</v>
+      </c>
+    </row>
+    <row r="8013">
+      <c r="A8013">
+        <v>1616832818</v>
+      </c>
+    </row>
+    <row r="8014">
+      <c r="A8014">
+        <v>1748776077</v>
+      </c>
+    </row>
+    <row r="8015">
+      <c r="A8015">
+        <v>1482931867</v>
+      </c>
+    </row>
+    <row r="8016">
+      <c r="A8016">
+        <v>729268014</v>
+      </c>
+    </row>
+    <row r="8017">
+      <c r="A8017">
+        <v>2088548668</v>
+      </c>
+    </row>
+    <row r="8018">
+      <c r="A8018">
+        <v>1319164159</v>
+      </c>
+    </row>
+    <row r="8019">
+      <c r="A8019">
+        <v>1953577794</v>
+      </c>
+    </row>
+    <row r="8020">
+      <c r="A8020">
+        <v>138512061</v>
+      </c>
+    </row>
+    <row r="8021">
+      <c r="A8021">
+        <v>1985010095</v>
+      </c>
+    </row>
+    <row r="8022">
+      <c r="A8022">
+        <v>1997899722</v>
+      </c>
+    </row>
+    <row r="8023">
+      <c r="A8023">
+        <v>971548889</v>
+      </c>
+    </row>
+    <row r="8024">
+      <c r="A8024">
+        <v>845983586</v>
+      </c>
+    </row>
+    <row r="8025">
+      <c r="A8025">
+        <v>459984355</v>
+      </c>
+    </row>
+    <row r="8026">
+      <c r="A8026">
+        <v>1363959813</v>
+      </c>
+    </row>
+    <row r="8027">
+      <c r="A8027">
+        <v>2090294284</v>
+      </c>
+    </row>
+    <row r="8028">
+      <c r="A8028">
+        <v>283798820</v>
+      </c>
+    </row>
+    <row r="8029">
+      <c r="A8029">
+        <v>1161773960</v>
+      </c>
+    </row>
+    <row r="8030">
+      <c r="A8030">
+        <v>1666107736</v>
+      </c>
+    </row>
+    <row r="8031">
+      <c r="A8031">
+        <v>911640270</v>
+      </c>
+    </row>
+    <row r="8032">
+      <c r="A8032">
+        <v>113406978</v>
+      </c>
+    </row>
+    <row r="8033">
+      <c r="A8033">
+        <v>1232939047</v>
+      </c>
+    </row>
+    <row r="8034">
+      <c r="A8034">
+        <v>353981346</v>
+      </c>
+    </row>
+    <row r="8035">
+      <c r="A8035">
+        <v>1483562403</v>
+      </c>
+    </row>
+    <row r="8036">
+      <c r="A8036">
+        <v>1882472351</v>
+      </c>
+    </row>
+    <row r="8037">
+      <c r="A8037">
+        <v>618715770</v>
+      </c>
+    </row>
+    <row r="8038">
+      <c r="A8038">
+        <v>1417034435</v>
+      </c>
+    </row>
+    <row r="8039">
+      <c r="A8039">
+        <v>1604655204</v>
+      </c>
+    </row>
+    <row r="8040">
+      <c r="A8040">
+        <v>1507145168</v>
+      </c>
+    </row>
+    <row r="8041">
+      <c r="A8041">
+        <v>2004834570</v>
+      </c>
+    </row>
+    <row r="8042">
+      <c r="A8042">
+        <v>814189724</v>
+      </c>
+    </row>
+    <row r="8043">
+      <c r="A8043">
+        <v>1855318052</v>
+      </c>
+    </row>
+    <row r="8044">
+      <c r="A8044">
+        <v>1670722184</v>
+      </c>
+    </row>
+    <row r="8045">
+      <c r="A8045">
+        <v>835224736</v>
+      </c>
+    </row>
+    <row r="8046">
+      <c r="A8046">
+        <v>1579637968</v>
+      </c>
+    </row>
+    <row r="8047">
+      <c r="A8047">
+        <v>497645253</v>
+      </c>
+    </row>
+    <row r="8048">
+      <c r="A8048">
+        <v>542894007</v>
+      </c>
+    </row>
+    <row r="8049">
+      <c r="A8049">
+        <v>115744700</v>
+      </c>
+    </row>
+    <row r="8050">
+      <c r="A8050">
+        <v>1813813653</v>
+      </c>
+    </row>
+    <row r="8051">
+      <c r="A8051">
+        <v>1145359542</v>
+      </c>
+    </row>
+    <row r="8052">
+      <c r="A8052">
+        <v>1898378584</v>
+      </c>
+    </row>
+    <row r="8053">
+      <c r="A8053">
+        <v>293430876</v>
+      </c>
+    </row>
+    <row r="8054">
+      <c r="A8054">
+        <v>502232178</v>
+      </c>
+    </row>
+    <row r="8055">
+      <c r="A8055">
+        <v>186993804</v>
+      </c>
+    </row>
+    <row r="8056">
+      <c r="A8056">
+        <v>1084887520</v>
+      </c>
+    </row>
+    <row r="8057">
+      <c r="A8057">
+        <v>63356908</v>
+      </c>
+    </row>
+    <row r="8058">
+      <c r="A8058">
+        <v>1256270279</v>
+      </c>
+    </row>
+    <row r="8059">
+      <c r="A8059">
+        <v>248053231</v>
+      </c>
+    </row>
+    <row r="8060">
+      <c r="A8060">
+        <v>1350257609</v>
+      </c>
+    </row>
+    <row r="8061">
+      <c r="A8061">
+        <v>851208983</v>
+      </c>
+    </row>
+    <row r="8062">
+      <c r="A8062">
+        <v>1341148035</v>
+      </c>
+    </row>
+    <row r="8063">
+      <c r="A8063">
+        <v>965999908</v>
+      </c>
+    </row>
+    <row r="8064">
+      <c r="A8064">
+        <v>1704315212</v>
+      </c>
+    </row>
+    <row r="8065">
+      <c r="A8065">
+        <v>289552162</v>
+      </c>
+    </row>
+    <row r="8066">
+      <c r="A8066">
+        <v>876590345</v>
+      </c>
+    </row>
+    <row r="8067">
+      <c r="A8067">
+        <v>475943429</v>
+      </c>
+    </row>
+    <row r="8068">
+      <c r="A8068">
+        <v>1789139866</v>
+      </c>
+    </row>
+    <row r="8069">
+      <c r="A8069">
+        <v>854350026</v>
+      </c>
+    </row>
+    <row r="8070">
+      <c r="A8070">
+        <v>338625907</v>
+      </c>
+    </row>
+    <row r="8071">
+      <c r="A8071">
+        <v>586342971</v>
+      </c>
+    </row>
+    <row r="8072">
+      <c r="A8072">
+        <v>1476628490</v>
+      </c>
+    </row>
+    <row r="8073">
+      <c r="A8073">
+        <v>2145781597</v>
+      </c>
+    </row>
+    <row r="8074">
+      <c r="A8074">
+        <v>1132832873</v>
+      </c>
+    </row>
+    <row r="8075">
+      <c r="A8075">
+        <v>1622313532</v>
+      </c>
+    </row>
+    <row r="8076">
+      <c r="A8076">
+        <v>102579106</v>
+      </c>
+    </row>
+    <row r="8077">
+      <c r="A8077">
+        <v>955821448</v>
+      </c>
+    </row>
+    <row r="8078">
+      <c r="A8078">
+        <v>2098989651</v>
+      </c>
+    </row>
+    <row r="8079">
+      <c r="A8079">
+        <v>1062220375</v>
+      </c>
+    </row>
+    <row r="8080">
+      <c r="A8080">
+        <v>390830394</v>
+      </c>
+    </row>
+    <row r="8081">
+      <c r="A8081">
+        <v>87537059</v>
+      </c>
+    </row>
+    <row r="8082">
+      <c r="A8082">
+        <v>119385149</v>
+      </c>
+    </row>
+    <row r="8083">
+      <c r="A8083">
+        <v>692476604</v>
+      </c>
+    </row>
+    <row r="8084">
+      <c r="A8084">
+        <v>268423526</v>
+      </c>
+    </row>
+    <row r="8085">
+      <c r="A8085">
+        <v>150881015</v>
+      </c>
+    </row>
+    <row r="8086">
+      <c r="A8086">
+        <v>1369393832</v>
+      </c>
+    </row>
+    <row r="8087">
+      <c r="A8087">
+        <v>1063749256</v>
+      </c>
+    </row>
+    <row r="8088">
+      <c r="A8088">
+        <v>766341938</v>
+      </c>
+    </row>
+    <row r="8089">
+      <c r="A8089">
+        <v>1395025483</v>
+      </c>
+    </row>
+    <row r="8090">
+      <c r="A8090">
+        <v>996327017</v>
+      </c>
+    </row>
+    <row r="8091">
+      <c r="A8091">
+        <v>447642807</v>
+      </c>
+    </row>
+    <row r="8092">
+      <c r="A8092">
+        <v>1756225142</v>
+      </c>
+    </row>
+    <row r="8093">
+      <c r="A8093">
+        <v>897646534</v>
+      </c>
+    </row>
+    <row r="8094">
+      <c r="A8094">
+        <v>1473017141</v>
+      </c>
+    </row>
+    <row r="8095">
+      <c r="A8095">
+        <v>164012970</v>
+      </c>
+    </row>
+    <row r="8096">
+      <c r="A8096">
+        <v>407897984</v>
+      </c>
+    </row>
+    <row r="8097">
+      <c r="A8097">
+        <v>1606922542</v>
+      </c>
+    </row>
+    <row r="8098">
+      <c r="A8098">
+        <v>117355054</v>
+      </c>
+    </row>
+    <row r="8099">
+      <c r="A8099">
+        <v>376970156</v>
+      </c>
+    </row>
+    <row r="8100">
+      <c r="A8100">
+        <v>1372337440</v>
+      </c>
+    </row>
+    <row r="8101">
+      <c r="A8101">
+        <v>742075914</v>
+      </c>
+    </row>
+    <row r="8102">
+      <c r="A8102">
+        <v>611471731</v>
+      </c>
+    </row>
+    <row r="8103">
+      <c r="A8103">
+        <v>249278952</v>
+      </c>
+    </row>
+    <row r="8104">
+      <c r="A8104">
+        <v>1274149726</v>
+      </c>
+    </row>
+    <row r="8105">
+      <c r="A8105">
+        <v>1238725518</v>
+      </c>
+    </row>
+    <row r="8106">
+      <c r="A8106">
+        <v>1537858146</v>
+      </c>
+    </row>
+    <row r="8107">
+      <c r="A8107">
+        <v>126169639</v>
+      </c>
+    </row>
+    <row r="8108">
+      <c r="A8108">
+        <v>2104187650</v>
+      </c>
+    </row>
+    <row r="8109">
+      <c r="A8109">
+        <v>810182882</v>
+      </c>
+    </row>
+    <row r="8110">
+      <c r="A8110">
+        <v>1328376555</v>
+      </c>
+    </row>
+    <row r="8111">
+      <c r="A8111">
+        <v>102202175</v>
+      </c>
+    </row>
+    <row r="8112">
+      <c r="A8112">
+        <v>998142026</v>
+      </c>
+    </row>
+    <row r="8113">
+      <c r="A8113">
+        <v>1592997453</v>
+      </c>
+    </row>
+    <row r="8114">
+      <c r="A8114">
+        <v>413933002</v>
+      </c>
+    </row>
+    <row r="8115">
+      <c r="A8115">
+        <v>811663911</v>
+      </c>
+    </row>
+    <row r="8116">
+      <c r="A8116">
+        <v>169240534</v>
+      </c>
+    </row>
+    <row r="8117">
+      <c r="A8117">
+        <v>847722591</v>
+      </c>
+    </row>
+    <row r="8118">
+      <c r="A8118">
+        <v>840762122</v>
+      </c>
+    </row>
+    <row r="8119">
+      <c r="A8119">
+        <v>1511841374</v>
+      </c>
+    </row>
+    <row r="8120">
+      <c r="A8120">
+        <v>1341558755</v>
+      </c>
+    </row>
+    <row r="8121">
+      <c r="A8121">
+        <v>1677071938</v>
+      </c>
+    </row>
+    <row r="8122">
+      <c r="A8122">
+        <v>1974091911</v>
+      </c>
+    </row>
+    <row r="8123">
+      <c r="A8123">
+        <v>1580606467</v>
+      </c>
+    </row>
+    <row r="8124">
+      <c r="A8124">
+        <v>774620867</v>
+      </c>
+    </row>
+    <row r="8125">
+      <c r="A8125">
+        <v>1444226154</v>
+      </c>
+    </row>
+    <row r="8126">
+      <c r="A8126">
+        <v>1616079418</v>
+      </c>
+    </row>
+    <row r="8127">
+      <c r="A8127">
+        <v>1397100845</v>
+      </c>
+    </row>
+    <row r="8128">
+      <c r="A8128">
+        <v>1886688201</v>
+      </c>
+    </row>
+    <row r="8129">
+      <c r="A8129">
+        <v>1081718299</v>
+      </c>
+    </row>
+    <row r="8130">
+      <c r="A8130">
+        <v>767338518</v>
+      </c>
+    </row>
+    <row r="8131">
+      <c r="A8131">
+        <v>1912075337</v>
+      </c>
+    </row>
+    <row r="8132">
+      <c r="A8132">
+        <v>478760431</v>
+      </c>
+    </row>
+    <row r="8133">
+      <c r="A8133">
+        <v>1313351413</v>
+      </c>
+    </row>
+    <row r="8134">
+      <c r="A8134">
+        <v>675570930</v>
+      </c>
+    </row>
+    <row r="8135">
+      <c r="A8135">
+        <v>190062657</v>
+      </c>
+    </row>
+    <row r="8136">
+      <c r="A8136">
+        <v>401743574</v>
+      </c>
+    </row>
+    <row r="8137">
+      <c r="A8137">
+        <v>1330523319</v>
+      </c>
+    </row>
+    <row r="8138">
+      <c r="A8138">
+        <v>2141714764</v>
+      </c>
+    </row>
+    <row r="8139">
+      <c r="A8139">
+        <v>496387322</v>
+      </c>
+    </row>
+    <row r="8140">
+      <c r="A8140">
+        <v>1226131960</v>
+      </c>
+    </row>
+    <row r="8141">
+      <c r="A8141">
+        <v>1074635535</v>
+      </c>
+    </row>
+    <row r="8142">
+      <c r="A8142">
+        <v>681990279</v>
+      </c>
+    </row>
+    <row r="8143">
+      <c r="A8143">
+        <v>1772353700</v>
+      </c>
+    </row>
+    <row r="8144">
+      <c r="A8144">
+        <v>1591502032</v>
+      </c>
+    </row>
+    <row r="8145">
+      <c r="A8145">
+        <v>1882524891</v>
+      </c>
+    </row>
+    <row r="8146">
+      <c r="A8146">
+        <v>284742297</v>
+      </c>
+    </row>
+    <row r="8147">
+      <c r="A8147">
+        <v>582102137</v>
+      </c>
+    </row>
+    <row r="8148">
+      <c r="A8148">
+        <v>1133747149</v>
+      </c>
+    </row>
+    <row r="8149">
+      <c r="A8149">
+        <v>732359973</v>
+      </c>
+    </row>
+    <row r="8150">
+      <c r="A8150">
+        <v>1443934162</v>
+      </c>
+    </row>
+    <row r="8151">
+      <c r="A8151">
+        <v>431545780</v>
+      </c>
+    </row>
+    <row r="8152">
+      <c r="A8152">
+        <v>2131184337</v>
+      </c>
+    </row>
+    <row r="8153">
+      <c r="A8153">
+        <v>630096546</v>
+      </c>
+    </row>
+    <row r="8154">
+      <c r="A8154">
+        <v>563523623</v>
+      </c>
+    </row>
+    <row r="8155">
+      <c r="A8155">
+        <v>1151797492</v>
+      </c>
+    </row>
+    <row r="8156">
+      <c r="A8156">
+        <v>312215167</v>
+      </c>
+    </row>
+    <row r="8157">
+      <c r="A8157">
+        <v>533808453</v>
+      </c>
+    </row>
+    <row r="8158">
+      <c r="A8158">
+        <v>1896247306</v>
+      </c>
+    </row>
+    <row r="8159">
+      <c r="A8159">
+        <v>1210836019</v>
+      </c>
+    </row>
+    <row r="8160">
+      <c r="A8160">
+        <v>1187456387</v>
+      </c>
+    </row>
+    <row r="8161">
+      <c r="A8161">
+        <v>480845740</v>
+      </c>
+    </row>
+    <row r="8162">
+      <c r="A8162">
+        <v>2043313101</v>
+      </c>
+    </row>
+    <row r="8163">
+      <c r="A8163">
+        <v>2087161745</v>
+      </c>
+    </row>
+    <row r="8164">
+      <c r="A8164">
+        <v>699563912</v>
+      </c>
+    </row>
+    <row r="8165">
+      <c r="A8165">
+        <v>228317751</v>
+      </c>
+    </row>
+    <row r="8166">
+      <c r="A8166">
+        <v>1675799403</v>
+      </c>
+    </row>
+    <row r="8167">
+      <c r="A8167">
+        <v>788089209</v>
+      </c>
+    </row>
+    <row r="8168">
+      <c r="A8168">
+        <v>1203797790</v>
+      </c>
+    </row>
+    <row r="8169">
+      <c r="A8169">
+        <v>1615642650</v>
+      </c>
+    </row>
+    <row r="8170">
+      <c r="A8170">
+        <v>1610607903</v>
+      </c>
+    </row>
+    <row r="8171">
+      <c r="A8171">
+        <v>1815306979</v>
+      </c>
+    </row>
+    <row r="8172">
+      <c r="A8172">
+        <v>467522128</v>
+      </c>
+    </row>
+    <row r="8173">
+      <c r="A8173">
+        <v>339113241</v>
+      </c>
+    </row>
+    <row r="8174">
+      <c r="A8174">
+        <v>483681810</v>
+      </c>
+    </row>
+    <row r="8175">
+      <c r="A8175">
+        <v>1720192353</v>
+      </c>
+    </row>
+    <row r="8176">
+      <c r="A8176">
+        <v>1730645862</v>
+      </c>
+    </row>
+    <row r="8177">
+      <c r="A8177">
+        <v>25336405</v>
+      </c>
+    </row>
+    <row r="8178">
+      <c r="A8178">
+        <v>1133336184</v>
+      </c>
+    </row>
+    <row r="8179">
+      <c r="A8179">
+        <v>235626078</v>
+      </c>
+    </row>
+    <row r="8180">
+      <c r="A8180">
+        <v>470408236</v>
+      </c>
+    </row>
+    <row r="8181">
+      <c r="A8181">
+        <v>532879140</v>
+      </c>
+    </row>
+    <row r="8182">
+      <c r="A8182">
+        <v>231365993</v>
+      </c>
+    </row>
+    <row r="8183">
+      <c r="A8183">
+        <v>1722860137</v>
+      </c>
+    </row>
+    <row r="8184">
+      <c r="A8184">
+        <v>205467526</v>
+      </c>
+    </row>
+    <row r="8185">
+      <c r="A8185">
+        <v>42792400</v>
+      </c>
+    </row>
+    <row r="8186">
+      <c r="A8186">
+        <v>395486366</v>
+      </c>
+    </row>
+    <row r="8187">
+      <c r="A8187">
+        <v>1904473186</v>
+      </c>
+    </row>
+    <row r="8188">
+      <c r="A8188">
+        <v>1402557029</v>
+      </c>
+    </row>
+    <row r="8189">
+      <c r="A8189">
+        <v>846437456</v>
+      </c>
+    </row>
+    <row r="8190">
+      <c r="A8190">
+        <v>308717138</v>
+      </c>
+    </row>
+    <row r="8191">
+      <c r="A8191">
+        <v>1798561391</v>
+      </c>
+    </row>
+    <row r="8192">
+      <c r="A8192">
+        <v>74216118</v>
+      </c>
+    </row>
+    <row r="8193">
+      <c r="A8193">
+        <v>1430995257</v>
+      </c>
+    </row>
+    <row r="8194">
+      <c r="A8194">
+        <v>1196824075</v>
+      </c>
+    </row>
+    <row r="8195">
+      <c r="A8195">
+        <v>1614600993</v>
+      </c>
+    </row>
+    <row r="8196">
+      <c r="A8196">
+        <v>162842834</v>
+      </c>
+    </row>
+    <row r="8197">
+      <c r="A8197">
+        <v>100174912</v>
+      </c>
+    </row>
+    <row r="8198">
+      <c r="A8198">
+        <v>1382913525</v>
+      </c>
+    </row>
+    <row r="8199">
+      <c r="A8199">
+        <v>1326912627</v>
+      </c>
+    </row>
+    <row r="8200">
+      <c r="A8200">
+        <v>758223983</v>
+      </c>
+    </row>
+    <row r="8201">
+      <c r="A8201">
+        <v>728569572</v>
+      </c>
+    </row>
+    <row r="8202">
+      <c r="A8202">
+        <v>2144349853</v>
+      </c>
+    </row>
+    <row r="8203">
+      <c r="A8203">
+        <v>1957347036</v>
+      </c>
+    </row>
+    <row r="8204">
+      <c r="A8204">
+        <v>1421424437</v>
+      </c>
+    </row>
+    <row r="8205">
+      <c r="A8205">
+        <v>57201508</v>
+      </c>
+    </row>
+    <row r="8206">
+      <c r="A8206">
+        <v>85400168</v>
+      </c>
+    </row>
+    <row r="8207">
+      <c r="A8207">
+        <v>629684864</v>
+      </c>
+    </row>
+    <row r="8208">
+      <c r="A8208">
+        <v>1104837242</v>
+      </c>
+    </row>
+    <row r="8209">
+      <c r="A8209">
+        <v>1836442293</v>
+      </c>
+    </row>
+    <row r="8210">
+      <c r="A8210">
+        <v>187061458</v>
+      </c>
+    </row>
+    <row r="8211">
+      <c r="A8211">
+        <v>1995715875</v>
+      </c>
+    </row>
+    <row r="8212">
+      <c r="A8212">
+        <v>883546182</v>
+      </c>
+    </row>
+    <row r="8213">
+      <c r="A8213">
+        <v>677350738</v>
+      </c>
+    </row>
+    <row r="8214">
+      <c r="A8214">
+        <v>1161710770</v>
+      </c>
+    </row>
+    <row r="8215">
+      <c r="A8215">
+        <v>1606433370</v>
+      </c>
+    </row>
+    <row r="8216">
+      <c r="A8216">
+        <v>1152094933</v>
+      </c>
+    </row>
+    <row r="8217">
+      <c r="A8217">
+        <v>2062604029</v>
+      </c>
+    </row>
+    <row r="8218">
+      <c r="A8218">
+        <v>866794353</v>
+      </c>
+    </row>
+    <row r="8219">
+      <c r="A8219">
+        <v>1483254129</v>
+      </c>
+    </row>
+    <row r="8220">
+      <c r="A8220">
+        <v>1163177632</v>
+      </c>
+    </row>
+    <row r="8221">
+      <c r="A8221">
+        <v>1713593695</v>
+      </c>
+    </row>
+    <row r="8222">
+      <c r="A8222">
+        <v>166561429</v>
+      </c>
+    </row>
+    <row r="8223">
+      <c r="A8223">
+        <v>1045891016</v>
+      </c>
+    </row>
+    <row r="8224">
+      <c r="A8224">
+        <v>1312035650</v>
+      </c>
+    </row>
+    <row r="8225">
+      <c r="A8225">
+        <v>1996702624</v>
+      </c>
+    </row>
+    <row r="8226">
+      <c r="A8226">
+        <v>649172507</v>
+      </c>
+    </row>
+    <row r="8227">
+      <c r="A8227">
+        <v>932108921</v>
+      </c>
+    </row>
+    <row r="8228">
+      <c r="A8228">
+        <v>2032936038</v>
+      </c>
+    </row>
+    <row r="8229">
+      <c r="A8229">
+        <v>1656590789</v>
+      </c>
+    </row>
+    <row r="8230">
+      <c r="A8230">
+        <v>663022179</v>
+      </c>
+    </row>
+    <row r="8231">
+      <c r="A8231">
+        <v>718346859</v>
+      </c>
+    </row>
+    <row r="8232">
+      <c r="A8232">
+        <v>113387330</v>
+      </c>
+    </row>
+    <row r="8233">
+      <c r="A8233">
+        <v>354648996</v>
+      </c>
+    </row>
+    <row r="8234">
+      <c r="A8234">
+        <v>942795987</v>
+      </c>
+    </row>
+    <row r="8235">
+      <c r="A8235">
+        <v>1253725904</v>
+      </c>
+    </row>
+    <row r="8236">
+      <c r="A8236">
+        <v>1172484027</v>
+      </c>
+    </row>
+    <row r="8237">
+      <c r="A8237">
+        <v>1464595591</v>
+      </c>
+    </row>
+    <row r="8238">
+      <c r="A8238">
+        <v>1833376905</v>
+      </c>
+    </row>
+    <row r="8239">
+      <c r="A8239">
+        <v>1038245373</v>
+      </c>
+    </row>
+    <row r="8240">
+      <c r="A8240">
+        <v>724200570</v>
+      </c>
+    </row>
+    <row r="8241">
+      <c r="A8241">
+        <v>746197086</v>
+      </c>
+    </row>
+    <row r="8242">
+      <c r="A8242">
+        <v>713245399</v>
+      </c>
+    </row>
+    <row r="8243">
+      <c r="A8243">
+        <v>1923148038</v>
+      </c>
+    </row>
+    <row r="8244">
+      <c r="A8244">
+        <v>909006938</v>
+      </c>
+    </row>
+    <row r="8245">
+      <c r="A8245">
+        <v>1172031772</v>
+      </c>
+    </row>
+    <row r="8246">
+      <c r="A8246">
+        <v>1922426945</v>
+      </c>
+    </row>
+    <row r="8247">
+      <c r="A8247">
+        <v>1412324237</v>
+      </c>
+    </row>
+    <row r="8248">
+      <c r="A8248">
+        <v>1713553670</v>
+      </c>
+    </row>
+    <row r="8249">
+      <c r="A8249">
+        <v>246918068</v>
+      </c>
+    </row>
+    <row r="8250">
+      <c r="A8250">
+        <v>1044292449</v>
+      </c>
+    </row>
+    <row r="8251">
+      <c r="A8251">
+        <v>1918433547</v>
+      </c>
+    </row>
+    <row r="8252">
+      <c r="A8252">
+        <v>264193860</v>
+      </c>
+    </row>
+    <row r="8253">
+      <c r="A8253">
+        <v>2035428132</v>
+      </c>
+    </row>
+    <row r="8254">
+      <c r="A8254">
+        <v>1883287316</v>
+      </c>
+    </row>
+    <row r="8255">
+      <c r="A8255">
+        <v>1551845884</v>
+      </c>
+    </row>
+    <row r="8256">
+      <c r="A8256">
+        <v>1013249157</v>
+      </c>
+    </row>
+    <row r="8257">
+      <c r="A8257">
+        <v>1725363859</v>
+      </c>
+    </row>
+    <row r="8258">
+      <c r="A8258">
+        <v>1688088090</v>
+      </c>
+    </row>
+    <row r="8259">
+      <c r="A8259">
+        <v>1445563756</v>
+      </c>
+    </row>
+    <row r="8260">
+      <c r="A8260">
+        <v>1963110969</v>
+      </c>
+    </row>
+    <row r="8261">
+      <c r="A8261">
+        <v>513549014</v>
+      </c>
+    </row>
+    <row r="8262">
+      <c r="A8262">
+        <v>427112458</v>
+      </c>
+    </row>
+    <row r="8263">
+      <c r="A8263">
+        <v>518325927</v>
+      </c>
+    </row>
+    <row r="8264">
+      <c r="A8264">
+        <v>1550015779</v>
+      </c>
+    </row>
+    <row r="8265">
+      <c r="A8265">
+        <v>898595308</v>
+      </c>
+    </row>
+    <row r="8266">
+      <c r="A8266">
+        <v>210464503</v>
+      </c>
+    </row>
+    <row r="8267">
+      <c r="A8267">
+        <v>2036335918</v>
+      </c>
+    </row>
+    <row r="8268">
+      <c r="A8268">
+        <v>156073536</v>
+      </c>
+    </row>
+    <row r="8269">
+      <c r="A8269">
+        <v>1039341788</v>
+      </c>
+    </row>
+    <row r="8270">
+      <c r="A8270">
+        <v>1259241498</v>
+      </c>
+    </row>
+    <row r="8271">
+      <c r="A8271">
+        <v>342711895</v>
+      </c>
+    </row>
+    <row r="8272">
+      <c r="A8272">
+        <v>152627832</v>
+      </c>
+    </row>
+    <row r="8273">
+      <c r="A8273">
+        <v>1423531729</v>
+      </c>
+    </row>
+    <row r="8274">
+      <c r="A8274">
+        <v>1727537526</v>
+      </c>
+    </row>
+    <row r="8275">
+      <c r="A8275">
+        <v>1151041143</v>
+      </c>
+    </row>
+    <row r="8276">
+      <c r="A8276">
+        <v>149346512</v>
+      </c>
+    </row>
+    <row r="8277">
+      <c r="A8277">
+        <v>992846381</v>
+      </c>
+    </row>
+    <row r="8278">
+      <c r="A8278">
+        <v>812236900</v>
+      </c>
+    </row>
+    <row r="8279">
+      <c r="A8279">
+        <v>615391081</v>
+      </c>
+    </row>
+    <row r="8280">
+      <c r="A8280">
+        <v>381212383</v>
+      </c>
+    </row>
+    <row r="8281">
+      <c r="A8281">
+        <v>1297235832</v>
+      </c>
+    </row>
+    <row r="8282">
+      <c r="A8282">
+        <v>2017918726</v>
+      </c>
+    </row>
+    <row r="8283">
+      <c r="A8283">
+        <v>1295990806</v>
+      </c>
+    </row>
+    <row r="8284">
+      <c r="A8284">
+        <v>675514072</v>
+      </c>
+    </row>
+    <row r="8285">
+      <c r="A8285">
+        <v>1755975241</v>
+      </c>
+    </row>
+    <row r="8286">
+      <c r="A8286">
+        <v>2012734143</v>
+      </c>
+    </row>
+    <row r="8287">
+      <c r="A8287">
+        <v>378711881</v>
+      </c>
+    </row>
+    <row r="8288">
+      <c r="A8288">
+        <v>747548767</v>
+      </c>
+    </row>
+    <row r="8289">
+      <c r="A8289">
+        <v>1983297567</v>
+      </c>
+    </row>
+    <row r="8290">
+      <c r="A8290">
+        <v>636551377</v>
+      </c>
+    </row>
+    <row r="8291">
+      <c r="A8291">
+        <v>899565006</v>
+      </c>
+    </row>
+    <row r="8292">
+      <c r="A8292">
+        <v>144742728</v>
+      </c>
+    </row>
+    <row r="8293">
+      <c r="A8293">
+        <v>1644814017</v>
+      </c>
+    </row>
+    <row r="8294">
+      <c r="A8294">
+        <v>1783070260</v>
+      </c>
+    </row>
+    <row r="8295">
+      <c r="A8295">
+        <v>1160327667</v>
+      </c>
+    </row>
+    <row r="8296">
+      <c r="A8296">
+        <v>527655606</v>
+      </c>
+    </row>
+    <row r="8297">
+      <c r="A8297">
+        <v>403354565</v>
+      </c>
+    </row>
+    <row r="8298">
+      <c r="A8298">
+        <v>1385999691</v>
+      </c>
+    </row>
+    <row r="8299">
+      <c r="A8299">
+        <v>1164485729</v>
+      </c>
+    </row>
+    <row r="8300">
+      <c r="A8300">
+        <v>759082630</v>
+      </c>
+    </row>
+    <row r="8301">
+      <c r="A8301">
+        <v>655249738</v>
+      </c>
+    </row>
+    <row r="8302">
+      <c r="A8302">
+        <v>1751054126</v>
+      </c>
+    </row>
+    <row r="8303">
+      <c r="A8303">
+        <v>2074965021</v>
+      </c>
+    </row>
+    <row r="8304">
+      <c r="A8304">
+        <v>91111533</v>
+      </c>
+    </row>
+    <row r="8305">
+      <c r="A8305">
+        <v>1387181431</v>
+      </c>
+    </row>
+    <row r="8306">
+      <c r="A8306">
+        <v>2036060911</v>
+      </c>
+    </row>
+    <row r="8307">
+      <c r="A8307">
+        <v>1097214882</v>
+      </c>
+    </row>
+    <row r="8308">
+      <c r="A8308">
+        <v>1125089828</v>
+      </c>
+    </row>
+    <row r="8309">
+      <c r="A8309">
+        <v>1993130559</v>
+      </c>
+    </row>
+    <row r="8310">
+      <c r="A8310">
+        <v>70351746</v>
+      </c>
+    </row>
+    <row r="8311">
+      <c r="A8311">
+        <v>1596396162</v>
+      </c>
+    </row>
+    <row r="8312">
+      <c r="A8312">
+        <v>503162539</v>
+      </c>
+    </row>
+    <row r="8313">
+      <c r="A8313">
+        <v>110566901</v>
+      </c>
+    </row>
+    <row r="8314">
+      <c r="A8314">
+        <v>257609096</v>
+      </c>
+    </row>
+    <row r="8315">
+      <c r="A8315">
+        <v>1163775961</v>
+      </c>
+    </row>
+    <row r="8316">
+      <c r="A8316">
+        <v>1652907714</v>
+      </c>
+    </row>
+    <row r="8317">
+      <c r="A8317">
+        <v>1291681791</v>
       </c>
     </row>
   </sheetData>
@@ -39516,3127 +41966,3127 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>124</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>-1447712242</v>
+        <v>1389192083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>281106408</v>
+        <v>618685506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>47196651</v>
+        <v>251526132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>-1846920567</v>
+        <v>-412060169</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1027355160</v>
+        <v>1526614509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>186530118</v>
+        <v>-176076156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>194983841</v>
+        <v>-1453167446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1253390899</v>
+        <v>1071757845</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>-581847134</v>
+        <v>-1435916625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>-542461292</v>
+        <v>-1252997962</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1562405143</v>
+        <v>1371476704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>67901197</v>
+        <v>-1728582109</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>1737068068</v>
+        <v>-851545791</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>-402065910</v>
+        <v>928058416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>1728180085</v>
+        <v>-648104370</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>-472081713</v>
+        <v>2028880569</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>427089366</v>
+        <v>1729443531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>-676826752</v>
+        <v>1374048122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>1773275587</v>
+        <v>-1931970948</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>692911969</v>
+        <v>1630646975</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>1634674128</v>
+        <v>6050709</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>601666862</v>
+        <v>-978988116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>-684907303</v>
+        <v>1442961794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>-1659863317</v>
+        <v>-1026515107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>144571226</v>
+        <v>-1593363881</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>-1568178916</v>
+        <v>372898110</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>102349855</v>
+        <v>-2067801736</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>808607861</v>
+        <v>229683803</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>-1034298100</v>
+        <v>2125206969</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>-768282398</v>
+        <v>-1703385080</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>-1474315843</v>
+        <v>-1067181386</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>-2006237641</v>
+        <v>529535473</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>2137863390</v>
+        <v>1537869859</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>1203908632</v>
+        <v>-78591886</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1889488763</v>
+        <v>-449537340</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>103649049</v>
+        <v>-1685721977</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1554969512</v>
+        <v>1006772317</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>569164630</v>
+        <v>-1032346028</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>351599569</v>
+        <v>-653343622</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>-2053566589</v>
+        <v>729935813</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>87505426</v>
+        <v>-319082209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>-176673372</v>
+        <v>-1896882010</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>1072552295</v>
+        <v>-919764432</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>1180681917</v>
+        <v>-736069421</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>1266495028</v>
+        <v>-644909327</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>-1751009894</v>
+        <v>1179571744</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>-352292379</v>
+        <v>-236732226</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>1181498751</v>
+        <v>1377584329</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>821654790</v>
+        <v>-703975813</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>477990544</v>
+        <v>-604562358</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>-1000929485</v>
+        <v>-1823316820</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>616813777</v>
+        <v>-1129888849</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>915771008</v>
+        <v>-1391630491</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>-181594274</v>
+        <v>1017134364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>1550906537</v>
+        <v>1080919410</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2102069083</v>
+        <v>226381293</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>-1806926486</v>
+        <v>1106772519</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>-772829172</v>
+        <v>964301390</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>865945679</v>
+        <v>-887351640</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>576037125</v>
+        <v>1560587435</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>-1987225156</v>
+        <v>-1682158135</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>-841479022</v>
+        <v>932889048</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>100317069</v>
+        <v>-1026836346</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>-1228525625</v>
+        <v>1841063265</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>-1403661138</v>
+        <v>486529267</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>621286664</v>
+        <v>1922647906</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>1984119563</v>
+        <v>-672214572</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>1230859753</v>
+        <v>-1070844713</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>2011577016</v>
+        <v>416773837</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>-588833434</v>
+        <v>-1400013212</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>416978433</v>
+        <v>-1379992502</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>-1767374701</v>
+        <v>1513052597</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>1835023170</v>
+        <v>185558287</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>221738228</v>
+        <v>416010774</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>1788305655</v>
+        <v>-1123447616</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>-1118119699</v>
+        <v>-1325479293</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>197090180</v>
+        <v>671200929</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>-1944848982</v>
+        <v>-536315760</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>-329848043</v>
+        <v>-1073917074</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>1551473071</v>
+        <v>1557257497</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>127703478</v>
+        <v>1098993067</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>-1200406560</v>
+        <v>1474382746</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>-2130178269</v>
+        <v>1910825820</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>1840865345</v>
+        <v>1957896799</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>-283100368</v>
+        <v>1934617141</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>-1829932722</v>
+        <v>-1137389108</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>-1847958599</v>
+        <v>-1060067038</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>-954591797</v>
+        <v>-568431747</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>555148922</v>
+        <v>1216645239</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>817580924</v>
+        <v>-203137634</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>-124533825</v>
+        <v>1115477080</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>1984277653</v>
+        <v>-1301147205</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>-691424596</v>
+        <v>1280206681</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>450850946</v>
+        <v>-1344912152</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>-558808995</v>
+        <v>1705536790</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>429324119</v>
+        <v>-625095023</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>730294846</v>
+        <v>1509245763</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>-1873977736</v>
+        <v>-1423163822</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>-483410597</v>
+        <v>-1501654812</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>-1864880967</v>
+        <v>-2125028569</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>-331889400</v>
+        <v>1345091453</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>-1199028298</v>
+        <v>-1553999244</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>1550118129</v>
+        <v>798958682</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>1469492003</v>
+        <v>641031333</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>402533746</v>
+        <v>-1893939521</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>-1124251708</v>
+        <v>-603038394</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>2118935431</v>
+        <v>-1980472368</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>-1451085475</v>
+        <v>-1132515853</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>-921931948</v>
+        <v>-1436505839</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>31864186</v>
+        <v>101078336</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>-765325115</v>
+        <v>654497054</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>1235464735</v>
+        <v>-829541911</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>-343362138</v>
+        <v>1689273115</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>-1121110224</v>
+        <v>-214315734</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>-2032845357</v>
+        <v>539477580</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>1183108081</v>
+        <v>-554016241</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>-1179177696</v>
+        <v>2124076357</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>-109335618</v>
+        <v>-308349188</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>624829385</v>
+        <v>1328303442</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>-1207471237</v>
+        <v>-642800947</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>1307922762</v>
+        <v>-913950073</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>-934396500</v>
+        <v>-2132206226</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>1429358767</v>
+        <v>885069640</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>1440371301</v>
+        <v>-944786613</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>-700020196</v>
+        <v>-711550295</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>1080337522</v>
+        <v>1081339896</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>-1441555731</v>
+        <v>498482982</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>-416807129</v>
+        <v>1223147585</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>-1866882226</v>
+        <v>93319635</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>231222184</v>
+        <v>-557655166</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>1515065259</v>
+        <v>1138880436</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>1837702345</v>
+        <v>1935927095</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>487714008</v>
+        <v>-1513832915</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>-885935738</v>
+        <v>-101929148</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>1093109857</v>
+        <v>-629855126</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>-1143412237</v>
+        <v>-18213163</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>-250767262</v>
+        <v>-976158609</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>-1579610412</v>
+        <v>596132214</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>1657395159</v>
+        <v>-1962423648</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>-1840708147</v>
+        <v>606828387</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>-446979740</v>
+        <v>2059721729</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>-409246390</v>
+        <v>977209200</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>-413211467</v>
+        <v>1368018702</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>725476367</v>
+        <v>-885085831</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>654933270</v>
+        <v>-1047454453</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>1325713344</v>
+        <v>-763107782</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>-1284082813</v>
+        <v>-161252036</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>1270333857</v>
+        <v>-856427905</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>-1228214896</v>
+        <v>-1751320107</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>502996590</v>
+        <v>-656820244</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>-730839015</v>
+        <v>-1073460926</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>-1379560277</v>
+        <v>-798599523</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>1227303066</v>
+        <v>374997783</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>-998426532</v>
+        <v>2109608574</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>-480266913</v>
+        <v>2002362936</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>2021539637</v>
+        <v>934098203</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>264540876</v>
+        <v>-2064203143</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>-116535262</v>
+        <v>-938737976</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>1105885821</v>
+        <v>-1707739402</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>-1063415945</v>
+        <v>-827531471</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>-1886863202</v>
+        <v>-2071062685</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>281313112</v>
+        <v>378883378</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>-1546769733</v>
+        <v>1374858884</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>-2055097255</v>
+        <v>-2022946105</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>710881256</v>
+        <v>-1546802787</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>-1822066154</v>
+        <v>684047636</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>-1241383535</v>
+        <v>1222906810</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>1861215811</v>
+        <v>32601605</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>411104594</v>
+        <v>-636635169</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>-665036316</v>
+        <v>-1932226970</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>-1027925977</v>
+        <v>1626249712</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>998204541</v>
+        <v>-1437468909</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>-877049484</v>
+        <v>1932474545</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>64914778</v>
+        <v>700476256</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>-1309486171</v>
+        <v>-1027303170</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>2002518975</v>
+        <v>1195362441</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>2101817414</v>
+        <v>-1678518341</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>248430288</v>
+        <v>1238618506</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>108185843</v>
+        <v>401064044</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>-1244750319</v>
+        <v>1204330991</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>-1986303936</v>
+        <v>-1898743259</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>1023220766</v>
+        <v>1107201756</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>-1584039191</v>
+        <v>284648626</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>1122656283</v>
+        <v>1912121261</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>-123197398</v>
+        <v>1595218791</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>-489637044</v>
+        <v>382318734</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>-1620289265</v>
+        <v>639858024</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>1939377221</v>
+        <v>-202807957</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>-322580996</v>
+        <v>802621193</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>-451576750</v>
+        <v>-182748776</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>126115277</v>
+        <v>-388325178</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>-889061497</v>
+        <v>2007564833</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>1080867438</v>
+        <v>-590345549</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>-1062979000</v>
+        <v>1499609122</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>-313242549</v>
+        <v>89031188</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>-145543767</v>
+        <v>522798743</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>423608568</v>
+        <v>-2051893107</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>1050944550</v>
+        <v>-286671452</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>1565402433</v>
+        <v>-1441792118</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>-1767402797</v>
+        <v>1510009845</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>698849922</v>
+        <v>-1412005297</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>1244741812</v>
+        <v>-1917405866</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>517419063</v>
+        <v>105295872</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>-843963603</v>
+        <v>-428945085</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>31529028</v>
+        <v>1197104353</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>-1967184534</v>
+        <v>-1403046320</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>-618458667</v>
+        <v>19122862</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>-1954527377</v>
+        <v>2009583193</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>165281398</v>
+        <v>-1096001941</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>-414699104</v>
+        <v>212425690</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>1788163683</v>
+        <v>-1712378724</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>1223085825</v>
+        <v>-1057970529</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>-1712046480</v>
+        <v>555461877</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>1223514638</v>
+        <v>-103985780</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>1544278649</v>
+        <v>-71493534</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>1411251723</v>
+        <v>1714632765</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>863784762</v>
+        <v>2098283191</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>-1703627204</v>
+        <v>1341737310</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>-978379393</v>
+        <v>216584344</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>-728781099</v>
+        <v>-1918100485</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>-103399700</v>
+        <v>1583745433</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>-1627418558</v>
+        <v>-893289944</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>-1982433379</v>
+        <v>647584470</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>-811203049</v>
+        <v>-1468838063</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>1520532350</v>
+        <v>1729237507</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>1278810424</v>
+        <v>538371474</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>735819291</v>
+        <v>38593316</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>221458400</v>
+        <v>196763570</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>671402956</v>
+        <v>-1824454672</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>-2137569824</v>
+        <v>534095300</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>-1743447518</v>
+        <v>372447576</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>-225159896</v>
+        <v>564131194</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>1789766924</v>
+        <v>1827100080</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>-49805764</v>
+        <v>-836814404</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>926439666</v>
+        <v>-148092332</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>514189040</v>
+        <v>-1783435838</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>-903282876</v>
+        <v>2089065248</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>-1590491560</v>
+        <v>971295676</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>1160825402</v>
+        <v>1426973776</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>-1934700816</v>
+        <v>-642199582</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>-409487172</v>
+        <v>-395422872</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>-699524588</v>
+        <v>-1742567604</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>-2038391614</v>
+        <v>-837506308</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>-579802016</v>
+        <v>1799256818</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>-1319694980</v>
+        <v>-181595904</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>-1068410672</v>
+        <v>-1686997900</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>543902754</v>
+        <v>-1350628856</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>-197106008</v>
+        <v>2042026426</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>349809548</v>
+        <v>145320400</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>2121029052</v>
+        <v>1349225452</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>-156146638</v>
+        <v>1685396</v>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>-391262400</v>
+        <v>-2016322350</v>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>-683498316</v>
+        <v>-1528231840</v>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>-365568184</v>
+        <v>-574729908</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>821146298</v>
+        <v>-1226787040</v>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>973225744</v>
+        <v>1229675138</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>-276544276</v>
+        <v>285977064</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>581299284</v>
+        <v>-2101513236</v>
       </c>
     </row>
     <row r="262">
       <c r="A262">
-        <v>-1989087470</v>
+        <v>-44806596</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>-1200627808</v>
+        <v>570157682</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>928392140</v>
+        <v>473509744</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>-687973536</v>
+        <v>-1737260764</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>1335289026</v>
+        <v>1219948088</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>-20169176</v>
+        <v>272571802</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>468680108</v>
+        <v>495683024</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>-380572868</v>
+        <v>-910171716</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>-2029496462</v>
+        <v>-1341844844</v>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>-723058896</v>
+        <v>-618404222</v>
       </c>
     </row>
     <row r="272">
       <c r="A272">
-        <v>-496568796</v>
+        <v>1154740672</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>-1765921736</v>
+        <v>-1506218180</v>
       </c>
     </row>
     <row r="274">
       <c r="A274">
-        <v>658598106</v>
+        <v>982853264</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>-1868137072</v>
+        <v>-1352797406</v>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>-1105962244</v>
+        <v>-2106227192</v>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>557196180</v>
+        <v>-1811089652</v>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>1004592962</v>
+        <v>-184461412</v>
       </c>
     </row>
     <row r="279">
       <c r="A279">
-        <v>-1166375424</v>
+        <v>-500805614</v>
       </c>
     </row>
     <row r="280">
       <c r="A280">
-        <v>1621978684</v>
+        <v>176825216</v>
       </c>
     </row>
     <row r="281">
       <c r="A281">
-        <v>1913066064</v>
+        <v>-567324908</v>
       </c>
     </row>
     <row r="282">
       <c r="A282">
-        <v>887103138</v>
+        <v>830712104</v>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>-1476474040</v>
+        <v>-276942790</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>-172367348</v>
+        <v>-1937553456</v>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>-1200105252</v>
+        <v>2064304748</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>1884592722</v>
+        <v>-878044108</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>1998059648</v>
+        <v>497812626</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>-1301986476</v>
+        <v>-634966688</v>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>-55882264</v>
+        <v>-707194548</v>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>380849914</v>
+        <v>-383911456</v>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>395889488</v>
+        <v>-1104302174</v>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>-1029927892</v>
+        <v>-835792984</v>
       </c>
     </row>
     <row r="293">
       <c r="A293">
-        <v>-372197004</v>
+        <v>-917986164</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>-127494510</v>
+        <v>-926473284</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>1815076448</v>
+        <v>1587771506</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>1265333900</v>
+        <v>-750394384</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>-94136480</v>
+        <v>-859348924</v>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>1786192610</v>
+        <v>382927960</v>
       </c>
     </row>
     <row r="299">
       <c r="A299">
-        <v>-1291759448</v>
+        <v>1137778746</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>-1659282228</v>
+        <v>955310192</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>-1035464196</v>
+        <v>-994266564</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>-1195022414</v>
+        <v>-1066583276</v>
       </c>
     </row>
     <row r="303">
       <c r="A303">
-        <v>-1768830480</v>
+        <v>1226186434</v>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>1632646596</v>
+        <v>-1262620960</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>-38702248</v>
+        <v>-225160068</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>-1605578886</v>
+        <v>936534224</v>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>-741513808</v>
+        <v>2060407714</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>-79553092</v>
+        <v>256983592</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>1747692628</v>
+        <v>-1840790260</v>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>282152898</v>
+        <v>-340390980</v>
       </c>
     </row>
     <row r="311">
       <c r="A311">
-        <v>-770697440</v>
+        <v>2086831410</v>
       </c>
     </row>
     <row r="312">
       <c r="A312">
-        <v>-1020648516</v>
+        <v>-405168960</v>
       </c>
     </row>
     <row r="313">
       <c r="A313">
-        <v>824761936</v>
+        <v>695127604</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>1312889314</v>
+        <v>-169396536</v>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>333522280</v>
+        <v>696276666</v>
       </c>
     </row>
     <row r="316">
       <c r="A316">
-        <v>-1140304564</v>
+        <v>608182416</v>
       </c>
     </row>
     <row r="317">
       <c r="A317">
-        <v>478231804</v>
+        <v>-2121856276</v>
       </c>
     </row>
     <row r="318">
       <c r="A318">
-        <v>-1092214030</v>
+        <v>1834711636</v>
       </c>
     </row>
     <row r="319">
       <c r="A319">
-        <v>-1931392256</v>
+        <v>2078162578</v>
       </c>
     </row>
     <row r="320">
       <c r="A320">
-        <v>1925901940</v>
+        <v>457177888</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>1056046088</v>
+        <v>1995541452</v>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>1463814586</v>
+        <v>165588192</v>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>1876339664</v>
+        <v>1407019714</v>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>1257035244</v>
+        <v>953364520</v>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>965345172</v>
+        <v>498289580</v>
       </c>
     </row>
     <row r="326">
       <c r="A326">
-        <v>1438666450</v>
+        <v>920259260</v>
       </c>
     </row>
     <row r="327">
       <c r="A327">
-        <v>-1326675360</v>
+        <v>1909863922</v>
       </c>
     </row>
     <row r="328">
       <c r="A328">
-        <v>-1789733556</v>
+        <v>1513784880</v>
       </c>
     </row>
     <row r="329">
       <c r="A329">
-        <v>95359264</v>
+        <v>-1992126556</v>
       </c>
     </row>
     <row r="330">
       <c r="A330">
-        <v>-154147198</v>
+        <v>665146808</v>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>1974699496</v>
+        <v>354778970</v>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>-1312334868</v>
+        <v>1067182224</v>
       </c>
     </row>
     <row r="333">
       <c r="A333">
-        <v>-800581060</v>
+        <v>637791100</v>
       </c>
     </row>
     <row r="334">
       <c r="A334">
-        <v>1547380338</v>
+        <v>-2029968620</v>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>-1181820048</v>
+        <v>-508169918</v>
       </c>
     </row>
     <row r="336">
       <c r="A336">
-        <v>-1321584348</v>
+        <v>1750090496</v>
       </c>
     </row>
     <row r="337">
       <c r="A337">
-        <v>-1907021256</v>
+        <v>-1441431620</v>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>-269669990</v>
+        <v>1666622288</v>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>1945841104</v>
+        <v>-1121487582</v>
       </c>
     </row>
     <row r="340">
       <c r="A340">
-        <v>1148784060</v>
+        <v>-102625720</v>
       </c>
     </row>
     <row r="341">
       <c r="A341">
-        <v>1145185428</v>
+        <v>2022217740</v>
       </c>
     </row>
     <row r="342">
       <c r="A342">
-        <v>1058558082</v>
+        <v>54337628</v>
       </c>
     </row>
     <row r="343">
       <c r="A343">
-        <v>856913344</v>
+        <v>644704722</v>
       </c>
     </row>
     <row r="344">
       <c r="A344">
-        <v>-1918302404</v>
+        <v>1528891904</v>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>529176720</v>
+        <v>941277524</v>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>32836386</v>
+        <v>1319122152</v>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>487227912</v>
+        <v>1842441466</v>
       </c>
     </row>
     <row r="348">
       <c r="A348">
-        <v>-2049310452</v>
+        <v>1900492496</v>
       </c>
     </row>
     <row r="349">
       <c r="A349">
-        <v>-773576292</v>
+        <v>1934302508</v>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>-1480222190</v>
+        <v>1860749556</v>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>-358228096</v>
+        <v>-1217378926</v>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>-307727596</v>
+        <v>923629920</v>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>-702637784</v>
+        <v>1535612940</v>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>1018273850</v>
+        <v>1588342496</v>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>374395856</v>
+        <v>-769635742</v>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>416188012</v>
+        <v>-1615733080</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>1963848244</v>
+        <v>670807628</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>-2040408430</v>
+        <v>-124511364</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>818482528</v>
+        <v>767399218</v>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>813474124</v>
+        <v>596729456</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>-591236128</v>
+        <v>806062916</v>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>1707524514</v>
+        <v>-190295080</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>-679157336</v>
+        <v>-397021318</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>-1097597300</v>
+        <v>791843376</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>-668338756</v>
+        <v>-1143370820</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>-1861934478</v>
+        <v>75293268</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>1249356784</v>
+        <v>-700117950</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>-932013500</v>
+        <v>-992348000</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>-767549352</v>
+        <v>-255003972</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>-2042842054</v>
+        <v>-1768776240</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>1913855088</v>
+        <v>600684386</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>-799898564</v>
+        <v>-1856654616</v>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>1891949844</v>
+        <v>159388876</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>1324344002</v>
+        <v>1887456764</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>-1001056544</v>
+        <v>-483018254</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>1866128508</v>
+        <v>884643456</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>2124284624</v>
+        <v>-1805466124</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>686580130</v>
+        <v>1601200776</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>943723560</v>
+        <v>-1246775494</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>663590668</v>
+        <v>1289117520</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>1379861948</v>
+        <v>-1496966036</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>-600168654</v>
+        <v>879848852</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>-1454043456</v>
+        <v>1315527762</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>-1825970124</v>
+        <v>-1199019552</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>2009018056</v>
+        <v>1854223564</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>538699962</v>
+        <v>-1360609120</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>-607993200</v>
+        <v>-1589646974</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>-1344395540</v>
+        <v>877508840</v>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>-1695428012</v>
+        <v>-1007439124</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>-1172599150</v>
+        <v>1861727548</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>2077054240</v>
+        <v>-1046774670</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>1204428236</v>
+        <v>-600152976</v>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>786231008</v>
+        <v>139602980</v>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>-1608565566</v>
+        <v>816726072</v>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>-970335192</v>
+        <v>-1641637094</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>-775511124</v>
+        <v>-928883504</v>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>1744078524</v>
+        <v>1052363580</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>1281738738</v>
+        <v>-1118636140</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>-812928464</v>
+        <v>-689418366</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>-64758876</v>
+        <v>805152192</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>776676792</v>
+        <v>1034334780</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>1594525530</v>
+        <v>998844816</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>1084692624</v>
+        <v>569420322</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>86206332</v>
+        <v>-87814904</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>923428116</v>
+        <v>-1960682868</v>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>1051410754</v>
+        <v>-1238628580</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>-399770368</v>
+        <v>-1724522350</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>1253859772</v>
+        <v>-798285440</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>-608494256</v>
+        <v>379814420</v>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>-1286829790</v>
+        <v>-1556004056</v>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>941552200</v>
+        <v>-318699974</v>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>1945295884</v>
+        <v>-2096117296</v>
       </c>
     </row>
     <row r="413">
       <c r="A413">
-        <v>619868764</v>
+        <v>6542700</v>
       </c>
     </row>
     <row r="414">
       <c r="A414">
-        <v>1758787026</v>
+        <v>-318200908</v>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>1981988352</v>
+        <v>1091062802</v>
       </c>
     </row>
     <row r="416">
       <c r="A416">
-        <v>-184970924</v>
+        <v>-1113198112</v>
       </c>
     </row>
     <row r="417">
       <c r="A417">
-        <v>106235112</v>
+        <v>1394082764</v>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>1839716602</v>
+        <v>1990820064</v>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>1896805072</v>
+        <v>138483746</v>
       </c>
     </row>
     <row r="420">
       <c r="A420">
-        <v>-1412931796</v>
+        <v>1575284008</v>
       </c>
     </row>
     <row r="421">
       <c r="A421">
-        <v>-1679016716</v>
+        <v>-1662257652</v>
       </c>
     </row>
     <row r="422">
       <c r="A422">
-        <v>-2145995374</v>
+        <v>-1927974084</v>
       </c>
     </row>
     <row r="423">
       <c r="A423">
-        <v>-2095421088</v>
+        <v>-1685552142</v>
       </c>
     </row>
     <row r="424">
       <c r="A424">
-        <v>-960681972</v>
+        <v>-1435123984</v>
       </c>
     </row>
     <row r="425">
       <c r="A425">
-        <v>1310320864</v>
+        <v>59046468</v>
       </c>
     </row>
     <row r="426">
       <c r="A426">
-        <v>-929241502</v>
+        <v>-1230004648</v>
       </c>
     </row>
     <row r="427">
       <c r="A427">
-        <v>-1296174936</v>
+        <v>-2133839046</v>
       </c>
     </row>
     <row r="428">
       <c r="A428">
-        <v>2136709196</v>
+        <v>1234420208</v>
       </c>
     </row>
     <row r="429">
       <c r="A429">
-        <v>-1769744516</v>
+        <v>-925655364</v>
       </c>
     </row>
     <row r="430">
       <c r="A430">
-        <v>-1718018766</v>
+        <v>-1080570604</v>
       </c>
     </row>
     <row r="431">
       <c r="A431">
-        <v>-1025012112</v>
+        <v>-1753448766</v>
       </c>
     </row>
     <row r="432">
       <c r="A432">
-        <v>1386088260</v>
+        <v>351428704</v>
       </c>
     </row>
     <row r="433">
       <c r="A433">
-        <v>-1255388200</v>
+        <v>1107642236</v>
       </c>
     </row>
     <row r="434">
       <c r="A434">
-        <v>-1274441862</v>
+        <v>706485200</v>
       </c>
     </row>
     <row r="435">
       <c r="A435">
-        <v>-1215708112</v>
+        <v>1657539874</v>
       </c>
     </row>
     <row r="436">
       <c r="A436">
-        <v>-925360196</v>
+        <v>2015291048</v>
       </c>
     </row>
     <row r="437">
       <c r="A437">
-        <v>1733778004</v>
+        <v>2095598476</v>
       </c>
     </row>
     <row r="438">
       <c r="A438">
-        <v>-759705534</v>
+        <v>-1134011204</v>
       </c>
     </row>
     <row r="439">
       <c r="A439">
-        <v>-1953556832</v>
+        <v>-1335773390</v>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>-364492100</v>
+        <v>-1526328768</v>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>-664238128</v>
+        <v>-1365276492</v>
       </c>
     </row>
     <row r="442">
       <c r="A442">
-        <v>1834477922</v>
+        <v>407464520</v>
       </c>
     </row>
     <row r="443">
       <c r="A443">
-        <v>348998376</v>
+        <v>997125562</v>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>1072960716</v>
+        <v>88125968</v>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>-234452484</v>
+        <v>-608731412</v>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>1544974834</v>
+        <v>-382935724</v>
       </c>
     </row>
     <row r="447">
       <c r="A447">
-        <v>-33681280</v>
+        <v>1221666066</v>
       </c>
     </row>
     <row r="448">
       <c r="A448">
-        <v>-843321868</v>
+        <v>-519399008</v>
       </c>
     </row>
     <row r="449">
       <c r="A449">
-        <v>1759120008</v>
+        <v>883424972</v>
       </c>
     </row>
     <row r="450">
       <c r="A450">
-        <v>-2050242758</v>
+        <v>1605564000</v>
       </c>
     </row>
     <row r="451">
       <c r="A451">
-        <v>398883152</v>
+        <v>2123342786</v>
       </c>
     </row>
     <row r="452">
       <c r="A452">
-        <v>-1005701012</v>
+        <v>819381032</v>
       </c>
     </row>
     <row r="453">
       <c r="A453">
-        <v>300074388</v>
+        <v>463707052</v>
       </c>
     </row>
     <row r="454">
       <c r="A454">
-        <v>-1011897262</v>
+        <v>874635068</v>
       </c>
     </row>
     <row r="455">
       <c r="A455">
-        <v>-938602016</v>
+        <v>446016882</v>
       </c>
     </row>
     <row r="456">
       <c r="A456">
-        <v>972652748</v>
+        <v>-1866440912</v>
       </c>
     </row>
     <row r="457">
       <c r="A457">
-        <v>-539776352</v>
+        <v>1436067108</v>
       </c>
     </row>
     <row r="458">
       <c r="A458">
-        <v>865896731</v>
+        <v>-1338449555</v>
       </c>
     </row>
     <row r="459">
       <c r="A459">
-        <v>-1273884948</v>
+        <v>-1442661609</v>
       </c>
     </row>
     <row r="460">
       <c r="A460">
-        <v>-604589318</v>
+        <v>-1906185504</v>
       </c>
     </row>
     <row r="461">
       <c r="A461">
-        <v>1594137391</v>
+        <v>241653950</v>
       </c>
     </row>
     <row r="462">
       <c r="A462">
-        <v>-518831303</v>
+        <v>-1138739573</v>
       </c>
     </row>
     <row r="463">
       <c r="A463">
-        <v>-419850930</v>
+        <v>1711820045</v>
       </c>
     </row>
     <row r="464">
       <c r="A464">
-        <v>-340860004</v>
+        <v>1768087866</v>
       </c>
     </row>
     <row r="465">
       <c r="A465">
-        <v>-320870131</v>
+        <v>-1786326664</v>
       </c>
     </row>
     <row r="466">
       <c r="A466">
-        <v>1664543607</v>
+        <v>185672481</v>
       </c>
     </row>
     <row r="467">
       <c r="A467">
-        <v>1087963008</v>
+        <v>1803367379</v>
       </c>
     </row>
     <row r="468">
       <c r="A468">
-        <v>-301797922</v>
+        <v>-375399692</v>
       </c>
     </row>
     <row r="469">
       <c r="A469">
-        <v>-1018359125</v>
+        <v>124351362</v>
       </c>
     </row>
     <row r="470">
       <c r="A470">
-        <v>-2093888083</v>
+        <v>782582295</v>
       </c>
     </row>
     <row r="471">
       <c r="A471">
-        <v>1715560986</v>
+        <v>-802557727</v>
       </c>
     </row>
     <row r="472">
       <c r="A472">
-        <v>-911018792</v>
+        <v>421453350</v>
       </c>
     </row>
     <row r="473">
       <c r="A473">
-        <v>1006614849</v>
+        <v>-1243187420</v>
       </c>
     </row>
     <row r="474">
       <c r="A474">
-        <v>-2033966605</v>
+        <v>-962504747</v>
       </c>
     </row>
     <row r="475">
       <c r="A475">
-        <v>60008468</v>
+        <v>-615870593</v>
       </c>
     </row>
     <row r="476">
       <c r="A476">
-        <v>-982618718</v>
+        <v>1224710680</v>
       </c>
     </row>
     <row r="477">
       <c r="A477">
-        <v>-1482331465</v>
+        <v>-30377674</v>
       </c>
     </row>
     <row r="478">
       <c r="A478">
-        <v>-458046335</v>
+        <v>-1207367741</v>
       </c>
     </row>
     <row r="479">
       <c r="A479">
-        <v>-882772858</v>
+        <v>42067461</v>
       </c>
     </row>
     <row r="480">
       <c r="A480">
-        <v>970928324</v>
+        <v>-922827358</v>
       </c>
     </row>
     <row r="481">
       <c r="A481">
-        <v>1140755957</v>
+        <v>1343883664</v>
       </c>
     </row>
     <row r="482">
       <c r="A482">
-        <v>-982722465</v>
+        <v>527479097</v>
       </c>
     </row>
     <row r="483">
       <c r="A483">
-        <v>111215288</v>
+        <v>-278477333</v>
       </c>
     </row>
     <row r="484">
       <c r="A484">
-        <v>-2130158698</v>
+        <v>1502889692</v>
       </c>
     </row>
     <row r="485">
       <c r="A485">
-        <v>-317085277</v>
+        <v>-932302070</v>
       </c>
     </row>
     <row r="486">
       <c r="A486">
-        <v>107683173</v>
+        <v>-2000937473</v>
       </c>
     </row>
     <row r="487">
       <c r="A487">
-        <v>803830914</v>
+        <v>757376073</v>
       </c>
     </row>
     <row r="488">
       <c r="A488">
-        <v>609555952</v>
+        <v>2025182686</v>
       </c>
     </row>
     <row r="489">
       <c r="A489">
-        <v>355558297</v>
+        <v>-1568823924</v>
       </c>
     </row>
     <row r="490">
       <c r="A490">
-        <v>-932854389</v>
+        <v>-104140451</v>
       </c>
     </row>
     <row r="491">
       <c r="A491">
-        <v>-70733700</v>
+        <v>1222855015</v>
       </c>
     </row>
     <row r="492">
       <c r="A492">
-        <v>-1702309206</v>
+        <v>1901255312</v>
       </c>
     </row>
     <row r="493">
       <c r="A493">
-        <v>-1624519457</v>
+        <v>357012654</v>
       </c>
     </row>
     <row r="494">
       <c r="A494">
-        <v>-1457288599</v>
+        <v>-249993893</v>
       </c>
     </row>
     <row r="495">
       <c r="A495">
-        <v>-910399362</v>
+        <v>2016790845</v>
       </c>
     </row>
     <row r="496">
       <c r="A496">
-        <v>-1920814996</v>
+        <v>546304938</v>
       </c>
     </row>
     <row r="497">
       <c r="A497">
-        <v>409389245</v>
+        <v>-798161848</v>
       </c>
     </row>
     <row r="498">
       <c r="A498">
-        <v>-340854393</v>
+        <v>292826225</v>
       </c>
     </row>
     <row r="499">
       <c r="A499">
-        <v>550890864</v>
+        <v>1376152035</v>
       </c>
     </row>
     <row r="500">
       <c r="A500">
-        <v>-1103636466</v>
+        <v>1188545764</v>
       </c>
     </row>
     <row r="501">
       <c r="A501">
-        <v>-765684421</v>
+        <v>1187717138</v>
       </c>
     </row>
     <row r="502">
       <c r="A502">
-        <v>-1080034787</v>
+        <v>1383371751</v>
       </c>
     </row>
     <row r="503">
       <c r="A503">
-        <v>597450442</v>
+        <v>-188023887</v>
       </c>
     </row>
     <row r="504">
       <c r="A504">
-        <v>2015107560</v>
+        <v>58152438</v>
       </c>
     </row>
     <row r="505">
       <c r="A505">
-        <v>-1532145967</v>
+        <v>-919095276</v>
       </c>
     </row>
     <row r="506">
       <c r="A506">
-        <v>-1826387261</v>
+        <v>176248613</v>
       </c>
     </row>
     <row r="507">
       <c r="A507">
-        <v>-685915708</v>
+        <v>662679599</v>
       </c>
     </row>
     <row r="508">
       <c r="A508">
-        <v>1344956018</v>
+        <v>519166440</v>
       </c>
     </row>
     <row r="509">
       <c r="A509">
-        <v>-863692985</v>
+        <v>118259398</v>
       </c>
     </row>
     <row r="510">
       <c r="A510">
-        <v>-142538991</v>
+        <v>1633845107</v>
       </c>
     </row>
     <row r="511">
       <c r="A511">
-        <v>748780182</v>
+        <v>-1058891819</v>
       </c>
     </row>
     <row r="512">
       <c r="A512">
-        <v>-13197324</v>
+        <v>-1813336142</v>
       </c>
     </row>
     <row r="513">
       <c r="A513">
-        <v>-1906890363</v>
+        <v>-1796261504</v>
       </c>
     </row>
     <row r="514">
       <c r="A514">
-        <v>1628873935</v>
+        <v>-161881751</v>
       </c>
     </row>
     <row r="515">
       <c r="A515">
-        <v>1719147976</v>
+        <v>-1653365285</v>
       </c>
     </row>
     <row r="516">
       <c r="A516">
-        <v>-1186466714</v>
+        <v>1049386284</v>
       </c>
     </row>
     <row r="517">
       <c r="A517">
-        <v>-231656813</v>
+        <v>-1094359238</v>
       </c>
     </row>
     <row r="518">
       <c r="A518">
-        <v>920222197</v>
+        <v>1346853359</v>
       </c>
     </row>
     <row r="519">
       <c r="A519">
-        <v>1908888530</v>
+        <v>-1812677511</v>
       </c>
     </row>
     <row r="520">
       <c r="A520">
-        <v>-112818144</v>
+        <v>601968398</v>
       </c>
     </row>
     <row r="521">
       <c r="A521">
-        <v>2071257609</v>
+        <v>-303019300</v>
       </c>
     </row>
     <row r="522">
       <c r="A522">
-        <v>1803877179</v>
+        <v>-2135783091</v>
       </c>
     </row>
     <row r="523">
       <c r="A523">
-        <v>-399618420</v>
+        <v>-1439218505</v>
       </c>
     </row>
     <row r="524">
       <c r="A524">
-        <v>-1836391654</v>
+        <v>794451520</v>
       </c>
     </row>
     <row r="525">
       <c r="A525">
-        <v>-1591089777</v>
+        <v>104009502</v>
       </c>
     </row>
     <row r="526">
       <c r="A526">
-        <v>-133874983</v>
+        <v>-174586389</v>
       </c>
     </row>
     <row r="527">
       <c r="A527">
-        <v>1919948142</v>
+        <v>2043967853</v>
       </c>
     </row>
     <row r="528">
       <c r="A528">
-        <v>-36325124</v>
+        <v>1116084186</v>
       </c>
     </row>
     <row r="529">
       <c r="A529">
-        <v>2048426605</v>
+        <v>-1694150248</v>
       </c>
     </row>
     <row r="530">
       <c r="A530">
-        <v>-491299305</v>
+        <v>-1165180927</v>
       </c>
     </row>
     <row r="531">
       <c r="A531">
-        <v>-388113440</v>
+        <v>-1068764749</v>
       </c>
     </row>
     <row r="532">
       <c r="A532">
-        <v>-1574295618</v>
+        <v>1671276756</v>
       </c>
     </row>
     <row r="533">
       <c r="A533">
-        <v>1054659979</v>
+        <v>833727970</v>
       </c>
     </row>
     <row r="534">
       <c r="A534">
-        <v>-740407795</v>
+        <v>-1622198153</v>
       </c>
     </row>
     <row r="535">
       <c r="A535">
-        <v>1235982906</v>
+        <v>143666625</v>
       </c>
     </row>
     <row r="536">
       <c r="A536">
-        <v>1655304824</v>
+        <v>1932592966</v>
       </c>
     </row>
     <row r="537">
       <c r="A537">
-        <v>-293578207</v>
+        <v>-266415484</v>
       </c>
     </row>
     <row r="538">
       <c r="A538">
-        <v>-411437869</v>
+        <v>-148898763</v>
       </c>
     </row>
     <row r="539">
       <c r="A539">
-        <v>1349743604</v>
+        <v>-357385185</v>
       </c>
     </row>
     <row r="540">
       <c r="A540">
-        <v>1035523202</v>
+        <v>-1607083144</v>
       </c>
     </row>
     <row r="541">
       <c r="A541">
-        <v>-1107362537</v>
+        <v>-2112839082</v>
       </c>
     </row>
     <row r="542">
       <c r="A542">
-        <v>199109601</v>
+        <v>-1998262557</v>
       </c>
     </row>
     <row r="543">
       <c r="A543">
-        <v>1237613862</v>
+        <v>1463290021</v>
       </c>
     </row>
     <row r="544">
       <c r="A544">
-        <v>1902394404</v>
+        <v>1643665730</v>
       </c>
     </row>
     <row r="545">
       <c r="A545">
-        <v>95041237</v>
+        <v>1403264816</v>
       </c>
     </row>
     <row r="546">
       <c r="A546">
-        <v>-558861697</v>
+        <v>-1294415015</v>
       </c>
     </row>
     <row r="547">
       <c r="A547">
-        <v>-1346952424</v>
+        <v>20717771</v>
       </c>
     </row>
     <row r="548">
       <c r="A548">
-        <v>2044377654</v>
+        <v>-1932250820</v>
       </c>
     </row>
     <row r="549">
       <c r="A549">
-        <v>-1203839805</v>
+        <v>924564842</v>
       </c>
     </row>
     <row r="550">
       <c r="A550">
-        <v>709488901</v>
+        <v>-1645684833</v>
       </c>
     </row>
     <row r="551">
       <c r="A551">
-        <v>-1595283294</v>
+        <v>1002881577</v>
       </c>
     </row>
     <row r="552">
       <c r="A552">
-        <v>638959248</v>
+        <v>-1016714050</v>
       </c>
     </row>
     <row r="553">
       <c r="A553">
-        <v>-860243399</v>
+        <v>1588770220</v>
       </c>
     </row>
     <row r="554">
       <c r="A554">
-        <v>-1347271957</v>
+        <v>-998618371</v>
       </c>
     </row>
     <row r="555">
       <c r="A555">
-        <v>2080031708</v>
+        <v>878839367</v>
       </c>
     </row>
     <row r="556">
       <c r="A556">
-        <v>1607050762</v>
+        <v>194106672</v>
       </c>
     </row>
     <row r="557">
       <c r="A557">
-        <v>2104531199</v>
+        <v>65971790</v>
       </c>
     </row>
     <row r="558">
       <c r="A558">
-        <v>1424145737</v>
+        <v>-335145349</v>
       </c>
     </row>
     <row r="559">
       <c r="A559">
-        <v>776236766</v>
+        <v>683021789</v>
       </c>
     </row>
     <row r="560">
       <c r="A560">
-        <v>-918760308</v>
+        <v>-571022326</v>
       </c>
     </row>
     <row r="561">
       <c r="A561">
-        <v>-1702108067</v>
+        <v>-1600735960</v>
       </c>
     </row>
     <row r="562">
       <c r="A562">
-        <v>-822863257</v>
+        <v>1174215569</v>
       </c>
     </row>
     <row r="563">
       <c r="A563">
-        <v>1107510160</v>
+        <v>58162563</v>
       </c>
     </row>
     <row r="564">
       <c r="A564">
-        <v>-1782110290</v>
+        <v>2013362820</v>
       </c>
     </row>
     <row r="565">
       <c r="A565">
-        <v>2061428315</v>
+        <v>1920420018</v>
       </c>
     </row>
     <row r="566">
       <c r="A566">
-        <v>1674377789</v>
+        <v>959027207</v>
       </c>
     </row>
     <row r="567">
       <c r="A567">
-        <v>-1209381718</v>
+        <v>-1757711279</v>
       </c>
     </row>
     <row r="568">
       <c r="A568">
-        <v>1068727624</v>
+        <v>-386718762</v>
       </c>
     </row>
     <row r="569">
       <c r="A569">
-        <v>-1113472655</v>
+        <v>814332596</v>
       </c>
     </row>
     <row r="570">
       <c r="A570">
-        <v>1067460323</v>
+        <v>-788526395</v>
       </c>
     </row>
     <row r="571">
       <c r="A571">
-        <v>1297411556</v>
+        <v>1010125839</v>
       </c>
     </row>
     <row r="572">
       <c r="A572">
-        <v>1184391442</v>
+        <v>-104092536</v>
       </c>
     </row>
     <row r="573">
       <c r="A573">
-        <v>-593306393</v>
+        <v>487759270</v>
       </c>
     </row>
     <row r="574">
       <c r="A574">
-        <v>1656154801</v>
+        <v>-182364845</v>
       </c>
     </row>
     <row r="575">
       <c r="A575">
-        <v>1597567222</v>
+        <v>1295036085</v>
       </c>
     </row>
     <row r="576">
       <c r="A576">
-        <v>-1729185004</v>
+        <v>-56327150</v>
       </c>
     </row>
     <row r="577">
       <c r="A577">
-        <v>666702885</v>
+        <v>1358345696</v>
       </c>
     </row>
     <row r="578">
       <c r="A578">
-        <v>-1168543441</v>
+        <v>698406985</v>
       </c>
     </row>
     <row r="579">
       <c r="A579">
-        <v>1766131432</v>
+        <v>1482997371</v>
       </c>
     </row>
     <row r="580">
       <c r="A580">
-        <v>-147082298</v>
+        <v>-547035316</v>
       </c>
     </row>
     <row r="581">
       <c r="A581">
-        <v>-43620749</v>
+        <v>1616114394</v>
       </c>
     </row>
     <row r="582">
       <c r="A582">
-        <v>1826539733</v>
+        <v>1181005519</v>
       </c>
     </row>
     <row r="583">
       <c r="A583">
-        <v>-135671118</v>
+        <v>-841197927</v>
       </c>
     </row>
     <row r="584">
       <c r="A584">
-        <v>65198720</v>
+        <v>-1490908498</v>
       </c>
     </row>
     <row r="585">
       <c r="A585">
-        <v>1411504745</v>
+        <v>-1514276932</v>
       </c>
     </row>
     <row r="586">
       <c r="A586">
-        <v>104337115</v>
+        <v>-1662160851</v>
       </c>
     </row>
     <row r="587">
       <c r="A587">
-        <v>-694195668</v>
+        <v>1128706007</v>
       </c>
     </row>
     <row r="588">
       <c r="A588">
-        <v>-1135074758</v>
+        <v>-589576672</v>
       </c>
     </row>
     <row r="589">
       <c r="A589">
-        <v>-1084494609</v>
+        <v>-1781962882</v>
       </c>
     </row>
     <row r="590">
       <c r="A590">
-        <v>-1025048711</v>
+        <v>779405643</v>
       </c>
     </row>
     <row r="591">
       <c r="A591">
-        <v>510592014</v>
+        <v>148171597</v>
       </c>
     </row>
     <row r="592">
       <c r="A592">
-        <v>-1024837156</v>
+        <v>65444218</v>
       </c>
     </row>
     <row r="593">
       <c r="A593">
-        <v>612768333</v>
+        <v>178092984</v>
       </c>
     </row>
     <row r="594">
       <c r="A594">
-        <v>1088891319</v>
+        <v>1982366049</v>
       </c>
     </row>
     <row r="595">
       <c r="A595">
-        <v>535217984</v>
+        <v>-1662186221</v>
       </c>
     </row>
     <row r="596">
       <c r="A596">
-        <v>-874889698</v>
+        <v>1632736564</v>
       </c>
     </row>
     <row r="597">
       <c r="A597">
-        <v>755878123</v>
+        <v>-2049507518</v>
       </c>
     </row>
     <row r="598">
       <c r="A598">
-        <v>27310189</v>
+        <v>-208445609</v>
       </c>
     </row>
     <row r="599">
       <c r="A599">
-        <v>1662439642</v>
+        <v>-1530515807</v>
       </c>
     </row>
     <row r="600">
       <c r="A600">
-        <v>1537732760</v>
+        <v>-1830518938</v>
       </c>
     </row>
     <row r="601">
       <c r="A601">
-        <v>-492779775</v>
+        <v>1665562980</v>
       </c>
     </row>
     <row r="602">
       <c r="A602">
-        <v>-1504424781</v>
+        <v>549903509</v>
       </c>
     </row>
     <row r="603">
       <c r="A603">
-        <v>-791877676</v>
+        <v>1334285759</v>
       </c>
     </row>
     <row r="604">
       <c r="A604">
-        <v>1291600610</v>
+        <v>1093581144</v>
       </c>
     </row>
     <row r="605">
       <c r="A605">
-        <v>-1480252553</v>
+        <v>43874166</v>
       </c>
     </row>
     <row r="606">
       <c r="A606">
-        <v>482594497</v>
+        <v>2052162947</v>
       </c>
     </row>
     <row r="607">
       <c r="A607">
-        <v>-199752122</v>
+        <v>649756613</v>
       </c>
     </row>
     <row r="608">
       <c r="A608">
-        <v>1310914948</v>
+        <v>689702114</v>
       </c>
     </row>
     <row r="609">
       <c r="A609">
-        <v>1127958325</v>
+        <v>369033552</v>
       </c>
     </row>
     <row r="610">
       <c r="A610">
-        <v>-1894075105</v>
+        <v>-801709959</v>
       </c>
     </row>
     <row r="611">
       <c r="A611">
-        <v>1013161080</v>
+        <v>-1579539541</v>
       </c>
     </row>
     <row r="612">
       <c r="A612">
-        <v>733563222</v>
+        <v>-1988376292</v>
       </c>
     </row>
     <row r="613">
       <c r="A613">
-        <v>-720197661</v>
+        <v>-724418998</v>
       </c>
     </row>
     <row r="614">
       <c r="A614">
-        <v>-1931791963</v>
+        <v>1954241087</v>
       </c>
     </row>
     <row r="615">
       <c r="A615">
-        <v>847307842</v>
+        <v>203460233</v>
       </c>
     </row>
     <row r="616">
       <c r="A616">
-        <v>-712295888</v>
+        <v>1801681566</v>
       </c>
     </row>
     <row r="617">
       <c r="A617">
-        <v>680399449</v>
+        <v>51464012</v>
       </c>
     </row>
     <row r="618">
       <c r="A618">
-        <v>1340113867</v>
+        <v>1983651613</v>
       </c>
     </row>
     <row r="619">
       <c r="A619">
-        <v>-1387748292</v>
+        <v>-1207525721</v>
       </c>
     </row>
     <row r="620">
       <c r="A620">
-        <v>1072474730</v>
+        <v>-919448112</v>
       </c>
     </row>
     <row r="621">
       <c r="A621">
-        <v>1119643807</v>
+        <v>1474661742</v>
       </c>
     </row>
     <row r="622">
       <c r="A622">
-        <v>-504708823</v>
+        <v>1498996763</v>
       </c>
     </row>
     <row r="623">
       <c r="A623">
-        <v>343299518</v>
+        <v>-1309126275</v>
       </c>
     </row>
     <row r="624">
       <c r="A624">
-        <v>1174545580</v>
+        <v>-355809430</v>
       </c>
     </row>
     <row r="625">
       <c r="A625">
-        <v>-811081219</v>
+        <v>-329219576</v>
       </c>
     </row>
     <row r="626">
       <c r="A626">
-        <v>-1690801849</v>
+        <v>1159587505</v>
       </c>
     </row>
     <row r="627">
       <c r="A627">
-        <v>-386330973</v>
+        <v>-543972138</v>
       </c>
     </row>
   </sheetData>
